--- a/research/traditional_assets/database/data/taiwan/taiwan_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_farming_agriculture.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07600297733566436</v>
+        <v>0.07588697138099303</v>
       </c>
       <c r="C2">
-        <v>75.52696976741291</v>
+        <v>75.03396801329365</v>
       </c>
       <c r="D2">
-        <v>73.6569697674129</v>
+        <v>73.94096801329364</v>
       </c>
       <c r="E2">
-        <v>-11.9</v>
+        <v>-11.123</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="G2">
         <v>1.87</v>
@@ -1585,28 +1585,28 @@
         <v>2.16</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0390831</v>
       </c>
       <c r="N2">
-        <v>2.16</v>
+        <v>2.1209169</v>
       </c>
       <c r="O2">
-        <v>0.4320000000000001</v>
+        <v>0.4241833800000001</v>
       </c>
       <c r="P2">
-        <v>1.728</v>
+        <v>1.69673352</v>
       </c>
       <c r="Q2">
-        <v>2.928</v>
+        <v>2.89673352</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07600297733566436</v>
+        <v>0.07624704179898285</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5934695157112746</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>55.26685447162584</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07588697138099303</v>
+        <v>0.07577096542632168</v>
       </c>
       <c r="C3">
-        <v>75.03396801329365</v>
+        <v>74.54316475276111</v>
       </c>
       <c r="D3">
-        <v>73.94096801329364</v>
+        <v>74.22716475276111</v>
       </c>
       <c r="E3">
-        <v>-11.123</v>
+        <v>-10.346</v>
       </c>
       <c r="F3">
-        <v>0.777</v>
+        <v>1.554</v>
       </c>
       <c r="G3">
         <v>1.87</v>
@@ -1667,28 +1667,28 @@
         <v>2.16</v>
       </c>
       <c r="M3">
-        <v>0.0390831</v>
+        <v>0.07816620000000001</v>
       </c>
       <c r="N3">
-        <v>2.1209169</v>
+        <v>2.0818338</v>
       </c>
       <c r="O3">
-        <v>0.4241833800000001</v>
+        <v>0.4163667600000001</v>
       </c>
       <c r="P3">
-        <v>1.69673352</v>
+        <v>1.66546704</v>
       </c>
       <c r="Q3">
-        <v>2.89673352</v>
+        <v>2.86546704</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07624704179898285</v>
+        <v>0.07649608716971601</v>
       </c>
       <c r="T3">
-        <v>0.5934695157112746</v>
+        <v>0.5983238735347687</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>55.26685447162584</v>
+        <v>27.63342723581292</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07577096542632168</v>
+        <v>0.07565495947165038</v>
       </c>
       <c r="C4">
-        <v>74.54316475276111</v>
+        <v>74.05458561355192</v>
       </c>
       <c r="D4">
-        <v>74.22716475276111</v>
+        <v>74.51558561355192</v>
       </c>
       <c r="E4">
-        <v>-10.346</v>
+        <v>-9.569000000000001</v>
       </c>
       <c r="F4">
-        <v>1.554</v>
+        <v>2.331</v>
       </c>
       <c r="G4">
         <v>1.87</v>
@@ -1749,28 +1749,28 @@
         <v>2.16</v>
       </c>
       <c r="M4">
-        <v>0.07816620000000001</v>
+        <v>0.1172493</v>
       </c>
       <c r="N4">
-        <v>2.0818338</v>
+        <v>2.0427507</v>
       </c>
       <c r="O4">
-        <v>0.4163667600000001</v>
+        <v>0.40855014</v>
       </c>
       <c r="P4">
-        <v>1.66546704</v>
+        <v>1.63420056</v>
       </c>
       <c r="Q4">
-        <v>2.86546704</v>
+        <v>2.83420056</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07649608716971601</v>
+        <v>0.07675026749654677</v>
       </c>
       <c r="T4">
-        <v>0.5983238735347687</v>
+        <v>0.6032783212102936</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>27.63342723581292</v>
+        <v>18.42228482387528</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07565495947165038</v>
+        <v>0.07553895351697903</v>
       </c>
       <c r="C5">
-        <v>74.05458561355192</v>
+        <v>73.56825662327859</v>
       </c>
       <c r="D5">
-        <v>74.51558561355192</v>
+        <v>74.80625662327859</v>
       </c>
       <c r="E5">
-        <v>-9.569000000000001</v>
+        <v>-8.792</v>
       </c>
       <c r="F5">
-        <v>2.331</v>
+        <v>3.108</v>
       </c>
       <c r="G5">
         <v>1.87</v>
@@ -1831,28 +1831,28 @@
         <v>2.16</v>
       </c>
       <c r="M5">
-        <v>0.1172493</v>
+        <v>0.1563324</v>
       </c>
       <c r="N5">
-        <v>2.0427507</v>
+        <v>2.0036676</v>
       </c>
       <c r="O5">
-        <v>0.40855014</v>
+        <v>0.40073352</v>
       </c>
       <c r="P5">
-        <v>1.63420056</v>
+        <v>1.60293408</v>
       </c>
       <c r="Q5">
-        <v>2.83420056</v>
+        <v>2.80293408</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07675026749654677</v>
+        <v>0.07700974324685317</v>
       </c>
       <c r="T5">
-        <v>0.6032783212102936</v>
+        <v>0.6083359865457254</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>18.42228482387528</v>
+        <v>13.81671361790646</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07553895351697903</v>
+        <v>0.07548294756230772</v>
       </c>
       <c r="C6">
-        <v>73.56825662327859</v>
+        <v>72.93240149471627</v>
       </c>
       <c r="D6">
-        <v>74.80625662327859</v>
+        <v>74.94740149471627</v>
       </c>
       <c r="E6">
-        <v>-8.792</v>
+        <v>-8.015000000000001</v>
       </c>
       <c r="F6">
-        <v>3.108</v>
+        <v>3.885</v>
       </c>
       <c r="G6">
         <v>1.87</v>
@@ -1913,45 +1913,45 @@
         <v>2.16</v>
       </c>
       <c r="M6">
-        <v>0.1563324</v>
+        <v>0.201243</v>
       </c>
       <c r="N6">
-        <v>2.0036676</v>
+        <v>1.958757</v>
       </c>
       <c r="O6">
-        <v>0.40073352</v>
+        <v>0.3917514</v>
       </c>
       <c r="P6">
-        <v>1.60293408</v>
+        <v>1.5670056</v>
       </c>
       <c r="Q6">
-        <v>2.80293408</v>
+        <v>2.7670056</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07700974324685317</v>
+        <v>0.07727468164453444</v>
       </c>
       <c r="T6">
-        <v>0.6083359865457254</v>
+        <v>0.6135001290461135</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.81671361790646</v>
+        <v>10.73329258657444</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07548294756230772</v>
+        <v>0.07546054160763638</v>
       </c>
       <c r="C7">
-        <v>72.93240149471627</v>
+        <v>72.21201772589775</v>
       </c>
       <c r="D7">
-        <v>74.94740149471627</v>
+        <v>75.00401772589775</v>
       </c>
       <c r="E7">
-        <v>-8.015000000000001</v>
+        <v>-7.238</v>
       </c>
       <c r="F7">
-        <v>3.885</v>
+        <v>4.662000000000001</v>
       </c>
       <c r="G7">
         <v>1.87</v>
@@ -1995,45 +1995,45 @@
         <v>2.16</v>
       </c>
       <c r="M7">
-        <v>0.201243</v>
+        <v>0.249417</v>
       </c>
       <c r="N7">
-        <v>1.958757</v>
+        <v>1.910583</v>
       </c>
       <c r="O7">
-        <v>0.3917514</v>
+        <v>0.3821166</v>
       </c>
       <c r="P7">
-        <v>1.5670056</v>
+        <v>1.5284664</v>
       </c>
       <c r="Q7">
-        <v>2.7670056</v>
+        <v>2.7284664</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07727468164453444</v>
+        <v>0.07754525702940041</v>
       </c>
       <c r="T7">
-        <v>0.6135001290461135</v>
+        <v>0.6187741469188505</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.73329258657444</v>
+        <v>8.660195576083426</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07546054160763638</v>
+        <v>0.07541493565296506</v>
       </c>
       <c r="C8">
-        <v>72.21201772589775</v>
+        <v>71.55052126345927</v>
       </c>
       <c r="D8">
-        <v>75.00401772589775</v>
+        <v>75.11952126345926</v>
       </c>
       <c r="E8">
-        <v>-7.238</v>
+        <v>-6.461</v>
       </c>
       <c r="F8">
-        <v>4.662</v>
+        <v>5.439</v>
       </c>
       <c r="G8">
         <v>1.87</v>
@@ -2077,45 +2077,45 @@
         <v>2.16</v>
       </c>
       <c r="M8">
-        <v>0.249417</v>
+        <v>0.2953377</v>
       </c>
       <c r="N8">
-        <v>1.910583</v>
+        <v>1.8646623</v>
       </c>
       <c r="O8">
-        <v>0.3821166</v>
+        <v>0.37293246</v>
       </c>
       <c r="P8">
-        <v>1.5284664</v>
+        <v>1.49172984</v>
       </c>
       <c r="Q8">
-        <v>2.7284664</v>
+        <v>2.69172984</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07754525702940041</v>
+        <v>0.07782165123974738</v>
       </c>
       <c r="T8">
-        <v>0.6187741469188505</v>
+        <v>0.6241615845307859</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.660195576083428</v>
+        <v>7.313661615161219</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07541493565296506</v>
+        <v>0.07533092969829373</v>
       </c>
       <c r="C9">
-        <v>71.55052126345926</v>
+        <v>70.9872120331933</v>
       </c>
       <c r="D9">
-        <v>75.11952126345926</v>
+        <v>75.33321203319329</v>
       </c>
       <c r="E9">
-        <v>-6.460999999999999</v>
+        <v>-5.684</v>
       </c>
       <c r="F9">
-        <v>5.439000000000001</v>
+        <v>6.216</v>
       </c>
       <c r="G9">
         <v>1.87</v>
@@ -2159,28 +2159,28 @@
         <v>2.16</v>
       </c>
       <c r="M9">
-        <v>0.2953377</v>
+        <v>0.3375288</v>
       </c>
       <c r="N9">
-        <v>1.8646623</v>
+        <v>1.8224712</v>
       </c>
       <c r="O9">
-        <v>0.37293246</v>
+        <v>0.36449424</v>
       </c>
       <c r="P9">
-        <v>1.49172984</v>
+        <v>1.45797696</v>
       </c>
       <c r="Q9">
-        <v>2.69172984</v>
+        <v>2.65797696</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07782165123974738</v>
+        <v>0.07810405401988449</v>
       </c>
       <c r="T9">
-        <v>0.6241615845307859</v>
+        <v>0.6296661403516765</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>7.313661615161219</v>
+        <v>6.399453913266067</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07533092969829373</v>
+        <v>0.07531892374362241</v>
       </c>
       <c r="C10">
-        <v>70.9872120331933</v>
+        <v>70.24085160314412</v>
       </c>
       <c r="D10">
-        <v>75.33321203319329</v>
+        <v>75.36385160314411</v>
       </c>
       <c r="E10">
-        <v>-5.684</v>
+        <v>-4.907</v>
       </c>
       <c r="F10">
-        <v>6.216</v>
+        <v>6.993</v>
       </c>
       <c r="G10">
         <v>1.87</v>
@@ -2241,45 +2241,45 @@
         <v>2.16</v>
       </c>
       <c r="M10">
-        <v>0.3375288</v>
+        <v>0.3867129</v>
       </c>
       <c r="N10">
-        <v>1.8224712</v>
+        <v>1.7732871</v>
       </c>
       <c r="O10">
-        <v>0.36449424</v>
+        <v>0.3546574200000001</v>
       </c>
       <c r="P10">
-        <v>1.45797696</v>
+        <v>1.41862968</v>
       </c>
       <c r="Q10">
-        <v>2.65797696</v>
+        <v>2.61862968</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07810405401988449</v>
+        <v>0.07839266345453011</v>
       </c>
       <c r="T10">
-        <v>0.6296661403516765</v>
+        <v>0.6352916754213778</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>6.399453913266067</v>
+        <v>5.585539039426924</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07531892374362241</v>
+        <v>0.07524291778895106</v>
       </c>
       <c r="C11">
-        <v>70.24085160314412</v>
+        <v>69.65840098611854</v>
       </c>
       <c r="D11">
-        <v>75.36385160314411</v>
+        <v>75.55840098611853</v>
       </c>
       <c r="E11">
-        <v>-4.907</v>
+        <v>-4.130000000000001</v>
       </c>
       <c r="F11">
-        <v>6.993</v>
+        <v>7.77</v>
       </c>
       <c r="G11">
         <v>1.87</v>
@@ -2323,28 +2323,28 @@
         <v>2.16</v>
       </c>
       <c r="M11">
-        <v>0.3867129</v>
+        <v>0.429681</v>
       </c>
       <c r="N11">
-        <v>1.7732871</v>
+        <v>1.730319</v>
       </c>
       <c r="O11">
-        <v>0.3546574200000001</v>
+        <v>0.3460638</v>
       </c>
       <c r="P11">
-        <v>1.41862968</v>
+        <v>1.3842552</v>
       </c>
       <c r="Q11">
-        <v>2.61862968</v>
+        <v>2.5842552</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07839266345453011</v>
+        <v>0.07868768643216785</v>
       </c>
       <c r="T11">
-        <v>0.6352916754213778</v>
+        <v>0.641042222381517</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.585539039426924</v>
+        <v>5.026985135484232</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07524291778895108</v>
+        <v>0.07516691183427973</v>
       </c>
       <c r="C12">
-        <v>69.65840098611849</v>
+        <v>69.07695741482294</v>
       </c>
       <c r="D12">
-        <v>75.55840098611849</v>
+        <v>75.75395741482293</v>
       </c>
       <c r="E12">
-        <v>-4.13</v>
+        <v>-3.353</v>
       </c>
       <c r="F12">
-        <v>7.77</v>
+        <v>8.547000000000001</v>
       </c>
       <c r="G12">
         <v>1.87</v>
@@ -2405,28 +2405,28 @@
         <v>2.16</v>
       </c>
       <c r="M12">
-        <v>0.429681</v>
+        <v>0.4726491</v>
       </c>
       <c r="N12">
-        <v>1.730319</v>
+        <v>1.6873509</v>
       </c>
       <c r="O12">
-        <v>0.3460638</v>
+        <v>0.3374701800000001</v>
       </c>
       <c r="P12">
-        <v>1.3842552</v>
+        <v>1.34988072</v>
       </c>
       <c r="Q12">
-        <v>2.5842552</v>
+        <v>2.54988072</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07868768643216786</v>
+        <v>0.07898933913964015</v>
       </c>
       <c r="T12">
-        <v>0.6410422223815171</v>
+        <v>0.6469219951160413</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.026985135484232</v>
+        <v>4.569986486803847</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07516691183427973</v>
+        <v>0.07533090587960842</v>
       </c>
       <c r="C13">
-        <v>69.07695741482294</v>
+        <v>67.8792727945556</v>
       </c>
       <c r="D13">
-        <v>75.75395741482293</v>
+        <v>75.3332727945556</v>
       </c>
       <c r="E13">
-        <v>-3.353</v>
+        <v>-2.576000000000001</v>
       </c>
       <c r="F13">
-        <v>8.547000000000001</v>
+        <v>9.324</v>
       </c>
       <c r="G13">
         <v>1.87</v>
@@ -2487,45 +2487,45 @@
         <v>2.16</v>
       </c>
       <c r="M13">
-        <v>0.4726491</v>
+        <v>0.5389272000000001</v>
       </c>
       <c r="N13">
-        <v>1.6873509</v>
+        <v>1.6210728</v>
       </c>
       <c r="O13">
-        <v>0.3374701800000001</v>
+        <v>0.32421456</v>
       </c>
       <c r="P13">
-        <v>1.34988072</v>
+        <v>1.29685824</v>
       </c>
       <c r="Q13">
-        <v>2.54988072</v>
+        <v>2.49685824</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07898933913964015</v>
+        <v>0.0792978475904641</v>
       </c>
       <c r="T13">
-        <v>0.6469219951160413</v>
+        <v>0.6529353990490777</v>
       </c>
       <c r="U13">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.569986486803847</v>
+        <v>4.007962485471136</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07533090587960842</v>
+        <v>0.07593009992493709</v>
       </c>
       <c r="C14">
-        <v>67.8792727945556</v>
+        <v>65.60412812905257</v>
       </c>
       <c r="D14">
-        <v>75.3332727945556</v>
+        <v>73.83512812905256</v>
       </c>
       <c r="E14">
-        <v>-2.576000000000001</v>
+        <v>-1.798999999999999</v>
       </c>
       <c r="F14">
-        <v>9.324</v>
+        <v>10.101</v>
       </c>
       <c r="G14">
         <v>1.87</v>
@@ -2569,45 +2569,45 @@
         <v>2.16</v>
       </c>
       <c r="M14">
-        <v>0.5389272000000001</v>
+        <v>0.6474741000000001</v>
       </c>
       <c r="N14">
-        <v>1.6210728</v>
+        <v>1.5125259</v>
       </c>
       <c r="O14">
-        <v>0.32421456</v>
+        <v>0.30250518</v>
       </c>
       <c r="P14">
-        <v>1.29685824</v>
+        <v>1.21002072</v>
       </c>
       <c r="Q14">
-        <v>2.49685824</v>
+        <v>2.410020719999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0792978475904641</v>
+        <v>0.07961344818958285</v>
       </c>
       <c r="T14">
-        <v>0.6529353990490777</v>
+        <v>0.6590870421529883</v>
       </c>
       <c r="U14">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04624</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.007962485471136</v>
+        <v>3.336040777538437</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07593009992493709</v>
+        <v>0.07592449397026575</v>
       </c>
       <c r="C15">
-        <v>65.60412812905257</v>
+        <v>64.84086832272526</v>
       </c>
       <c r="D15">
-        <v>73.83512812905256</v>
+        <v>73.84886832272525</v>
       </c>
       <c r="E15">
-        <v>-1.798999999999999</v>
+        <v>-1.021999999999998</v>
       </c>
       <c r="F15">
-        <v>10.101</v>
+        <v>10.878</v>
       </c>
       <c r="G15">
         <v>1.87</v>
@@ -2651,28 +2651,28 @@
         <v>2.16</v>
       </c>
       <c r="M15">
-        <v>0.6474741000000001</v>
+        <v>0.6972798000000001</v>
       </c>
       <c r="N15">
-        <v>1.5125259</v>
+        <v>1.4627202</v>
       </c>
       <c r="O15">
-        <v>0.30250518</v>
+        <v>0.2925440400000001</v>
       </c>
       <c r="P15">
-        <v>1.21002072</v>
+        <v>1.17017616</v>
       </c>
       <c r="Q15">
-        <v>2.410020719999999</v>
+        <v>2.37017616</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07961344818958285</v>
+        <v>0.07993638833751832</v>
       </c>
       <c r="T15">
-        <v>0.6590870421529883</v>
+        <v>0.6653817467244318</v>
       </c>
       <c r="U15">
         <v>0.0641</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>3.336040777538437</v>
+        <v>3.097752150571406</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07592449397026575</v>
+        <v>0.07685488801559441</v>
       </c>
       <c r="C16">
-        <v>64.84086832272526</v>
+        <v>61.85138095818473</v>
       </c>
       <c r="D16">
-        <v>73.84886832272525</v>
+        <v>71.63638095818473</v>
       </c>
       <c r="E16">
-        <v>-1.021999999999998</v>
+        <v>-0.2449999999999974</v>
       </c>
       <c r="F16">
-        <v>10.878</v>
+        <v>11.655</v>
       </c>
       <c r="G16">
         <v>1.87</v>
@@ -2733,45 +2733,45 @@
         <v>2.16</v>
       </c>
       <c r="M16">
-        <v>0.6972798000000001</v>
+        <v>0.8379945000000003</v>
       </c>
       <c r="N16">
-        <v>1.4627202</v>
+        <v>1.3220055</v>
       </c>
       <c r="O16">
-        <v>0.2925440400000001</v>
+        <v>0.2644011</v>
       </c>
       <c r="P16">
-        <v>1.17017616</v>
+        <v>1.0576044</v>
       </c>
       <c r="Q16">
-        <v>2.37017616</v>
+        <v>2.2576044</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07993638833751832</v>
+        <v>0.0802669270771699</v>
       </c>
       <c r="T16">
-        <v>0.6653817467244318</v>
+        <v>0.6718245619916738</v>
       </c>
       <c r="U16">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.097752150571406</v>
+        <v>2.577582549766138</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07685488801559441</v>
+        <v>0.0774108820609231</v>
       </c>
       <c r="C17">
-        <v>61.85138095818473</v>
+        <v>59.81439076984118</v>
       </c>
       <c r="D17">
-        <v>71.63638095818473</v>
+        <v>70.37639076984118</v>
       </c>
       <c r="E17">
-        <v>-0.245000000000001</v>
+        <v>0.532</v>
       </c>
       <c r="F17">
-        <v>11.655</v>
+        <v>12.432</v>
       </c>
       <c r="G17">
         <v>1.87</v>
@@ -2815,45 +2815,45 @@
         <v>2.16</v>
       </c>
       <c r="M17">
-        <v>0.8379945</v>
+        <v>0.9423456000000001</v>
       </c>
       <c r="N17">
-        <v>1.3220055</v>
+        <v>1.2176544</v>
       </c>
       <c r="O17">
-        <v>0.2644011000000001</v>
+        <v>0.24353088</v>
       </c>
       <c r="P17">
-        <v>1.0576044</v>
+        <v>0.97412352</v>
       </c>
       <c r="Q17">
-        <v>2.2576044</v>
+        <v>2.17412352</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0802669270771699</v>
+        <v>0.08060533578681321</v>
       </c>
       <c r="T17">
-        <v>0.6718245619916738</v>
+        <v>0.6784207776224218</v>
       </c>
       <c r="U17">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.577582549766138</v>
+        <v>2.292152687931052</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0774108820609231</v>
+        <v>0.07749887610625178</v>
       </c>
       <c r="C18">
-        <v>59.81439076984118</v>
+        <v>58.84203042650557</v>
       </c>
       <c r="D18">
-        <v>70.37639076984118</v>
+        <v>70.18103042650557</v>
       </c>
       <c r="E18">
-        <v>0.532</v>
+        <v>1.309000000000001</v>
       </c>
       <c r="F18">
-        <v>12.432</v>
+        <v>13.209</v>
       </c>
       <c r="G18">
         <v>1.87</v>
@@ -2897,28 +2897,28 @@
         <v>2.16</v>
       </c>
       <c r="M18">
-        <v>0.9423456000000001</v>
+        <v>1.0012422</v>
       </c>
       <c r="N18">
-        <v>1.2176544</v>
+        <v>1.1587578</v>
       </c>
       <c r="O18">
-        <v>0.24353088</v>
+        <v>0.23175156</v>
       </c>
       <c r="P18">
-        <v>0.97412352</v>
+        <v>0.9270062400000001</v>
       </c>
       <c r="Q18">
-        <v>2.17412352</v>
+        <v>2.12700624</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08060533578681321</v>
+        <v>0.0809518989231949</v>
       </c>
       <c r="T18">
-        <v>0.6784207776224218</v>
+        <v>0.6851759382081275</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.292152687931052</v>
+        <v>2.157320176876284</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07749887610625178</v>
+        <v>0.07758687015158044</v>
       </c>
       <c r="C19">
-        <v>58.84203042650557</v>
+        <v>57.87075169622752</v>
       </c>
       <c r="D19">
-        <v>70.18103042650557</v>
+        <v>69.98675169622751</v>
       </c>
       <c r="E19">
-        <v>1.309000000000001</v>
+        <v>2.086000000000002</v>
       </c>
       <c r="F19">
-        <v>13.209</v>
+        <v>13.986</v>
       </c>
       <c r="G19">
         <v>1.87</v>
@@ -2979,28 +2979,28 @@
         <v>2.16</v>
       </c>
       <c r="M19">
-        <v>1.0012422</v>
+        <v>1.0601388</v>
       </c>
       <c r="N19">
-        <v>1.1587578</v>
+        <v>1.0998612</v>
       </c>
       <c r="O19">
-        <v>0.23175156</v>
+        <v>0.21997224</v>
       </c>
       <c r="P19">
-        <v>0.9270062400000001</v>
+        <v>0.8798889599999999</v>
       </c>
       <c r="Q19">
-        <v>2.12700624</v>
+        <v>2.07988896</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0809518989231949</v>
+        <v>0.08130691481900054</v>
       </c>
       <c r="T19">
-        <v>0.6851759382081275</v>
+        <v>0.6920958588081187</v>
       </c>
       <c r="U19">
         <v>0.07580000000000001</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>2.157320176876284</v>
+        <v>2.037469055938713</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07758687015158044</v>
+        <v>0.07983326419690912</v>
       </c>
       <c r="C20">
-        <v>57.87075169622752</v>
+        <v>52.47421766174076</v>
       </c>
       <c r="D20">
-        <v>69.98675169622751</v>
+        <v>65.36721766174075</v>
       </c>
       <c r="E20">
-        <v>2.086</v>
+        <v>2.863</v>
       </c>
       <c r="F20">
-        <v>13.986</v>
+        <v>14.763</v>
       </c>
       <c r="G20">
         <v>1.87</v>
@@ -3061,45 +3061,45 @@
         <v>2.16</v>
       </c>
       <c r="M20">
-        <v>1.0601388</v>
+        <v>1.32867</v>
       </c>
       <c r="N20">
-        <v>1.0998612</v>
+        <v>0.8313300000000001</v>
       </c>
       <c r="O20">
-        <v>0.21997224</v>
+        <v>0.166266</v>
       </c>
       <c r="P20">
-        <v>0.8798889600000001</v>
+        <v>0.6650640000000001</v>
       </c>
       <c r="Q20">
-        <v>2.07988896</v>
+        <v>1.865064</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08130691481900054</v>
+        <v>0.08167069653939396</v>
       </c>
       <c r="T20">
-        <v>0.6920958588081186</v>
+        <v>0.6991866416451468</v>
       </c>
       <c r="U20">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.037469055938713</v>
+        <v>1.625685836212152</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07983326419690912</v>
+        <v>0.08003485824223779</v>
       </c>
       <c r="C21">
-        <v>52.47421766174076</v>
+        <v>51.31229882413178</v>
       </c>
       <c r="D21">
-        <v>65.36721766174075</v>
+        <v>64.98229882413177</v>
       </c>
       <c r="E21">
-        <v>2.863</v>
+        <v>3.640000000000001</v>
       </c>
       <c r="F21">
-        <v>14.763</v>
+        <v>15.54</v>
       </c>
       <c r="G21">
         <v>1.87</v>
@@ -3143,28 +3143,28 @@
         <v>2.16</v>
       </c>
       <c r="M21">
-        <v>1.32867</v>
+        <v>1.3986</v>
       </c>
       <c r="N21">
-        <v>0.8313300000000001</v>
+        <v>0.7614000000000001</v>
       </c>
       <c r="O21">
-        <v>0.166266</v>
+        <v>0.15228</v>
       </c>
       <c r="P21">
-        <v>0.6650640000000001</v>
+        <v>0.6091200000000001</v>
       </c>
       <c r="Q21">
-        <v>1.865064</v>
+        <v>1.80912</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08167069653939396</v>
+        <v>0.08204357280279723</v>
       </c>
       <c r="T21">
-        <v>0.6991866416451468</v>
+        <v>0.7064546940531004</v>
       </c>
       <c r="U21">
         <v>0.09</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>1.625685836212152</v>
+        <v>1.544401544401544</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08003485824223779</v>
+        <v>0.09050923607122882</v>
       </c>
       <c r="C22">
-        <v>51.31229882413178</v>
+        <v>35.31139410350592</v>
       </c>
       <c r="D22">
-        <v>64.98229882413177</v>
+        <v>49.75839410350593</v>
       </c>
       <c r="E22">
-        <v>3.640000000000001</v>
+        <v>4.417000000000003</v>
       </c>
       <c r="F22">
-        <v>15.54</v>
+        <v>16.317</v>
       </c>
       <c r="G22">
         <v>1.87</v>
@@ -3225,45 +3225,45 @@
         <v>2.16</v>
       </c>
       <c r="M22">
-        <v>1.3986</v>
+        <v>2.395335600000001</v>
       </c>
       <c r="N22">
-        <v>0.7614000000000001</v>
+        <v>-0.2353356000000004</v>
       </c>
       <c r="O22">
-        <v>0.15228</v>
+        <v>-0.04706712000000009</v>
       </c>
       <c r="P22">
-        <v>0.6091200000000001</v>
+        <v>-0.1882684800000003</v>
       </c>
       <c r="Q22">
-        <v>1.80912</v>
+        <v>1.011731519999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08204357280279723</v>
+        <v>0.08258364763427137</v>
       </c>
       <c r="T22">
-        <v>0.7064546940531004</v>
+        <v>0.7169817577592865</v>
       </c>
       <c r="U22">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.2</v>
+        <v>0.1803505112185532</v>
       </c>
       <c r="W22">
-        <v>0.07199999999999999</v>
+        <v>0.1203245449531164</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y22">
-        <v>1.544401544401544</v>
+        <v>0.9017525560927662</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09050923607122881</v>
+        <v>0.0915192360712288</v>
       </c>
       <c r="C23">
-        <v>35.31139410350593</v>
+        <v>33.4351636184155</v>
       </c>
       <c r="D23">
-        <v>49.75839410350594</v>
+        <v>48.6591636184155</v>
       </c>
       <c r="E23">
-        <v>4.417</v>
+        <v>5.194000000000001</v>
       </c>
       <c r="F23">
-        <v>16.317</v>
+        <v>17.094</v>
       </c>
       <c r="G23">
         <v>1.87</v>
@@ -3307,37 +3307,37 @@
         <v>2.16</v>
       </c>
       <c r="M23">
-        <v>2.3953356</v>
+        <v>2.5093992</v>
       </c>
       <c r="N23">
-        <v>-0.2353356</v>
+        <v>-0.3493992000000001</v>
       </c>
       <c r="O23">
-        <v>-0.04706712</v>
+        <v>-0.06987984000000003</v>
       </c>
       <c r="P23">
-        <v>-0.18826848</v>
+        <v>-0.2795193600000001</v>
       </c>
       <c r="Q23">
-        <v>1.01173152</v>
+        <v>0.9204806399999996</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08258364763427135</v>
+        <v>0.08305523286035175</v>
       </c>
       <c r="T23">
-        <v>0.7169817577592863</v>
+        <v>0.7261738315767131</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.1803505112185533</v>
+        <v>0.172152760708619</v>
       </c>
       <c r="W23">
-        <v>0.1203245449531164</v>
+        <v>0.1215279747279747</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.9017525560927663</v>
+        <v>0.8607638035430951</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0915192360712288</v>
+        <v>0.09252923607122882</v>
       </c>
       <c r="C24">
-        <v>33.4351636184155</v>
+        <v>31.60645040017056</v>
       </c>
       <c r="D24">
-        <v>48.6591636184155</v>
+        <v>47.60745040017056</v>
       </c>
       <c r="E24">
-        <v>5.194000000000001</v>
+        <v>5.971000000000002</v>
       </c>
       <c r="F24">
-        <v>17.094</v>
+        <v>17.871</v>
       </c>
       <c r="G24">
         <v>1.87</v>
@@ -3389,37 +3389,37 @@
         <v>2.16</v>
       </c>
       <c r="M24">
-        <v>2.5093992</v>
+        <v>2.6234628</v>
       </c>
       <c r="N24">
-        <v>-0.3493992000000001</v>
+        <v>-0.4634628000000003</v>
       </c>
       <c r="O24">
-        <v>-0.06987984000000003</v>
+        <v>-0.09269256000000006</v>
       </c>
       <c r="P24">
-        <v>-0.2795193600000001</v>
+        <v>-0.3707702400000003</v>
       </c>
       <c r="Q24">
-        <v>0.9204806399999996</v>
+        <v>0.8292297599999995</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08305523286035175</v>
+        <v>0.08353906705334334</v>
       </c>
       <c r="T24">
-        <v>0.7261738315767131</v>
+        <v>0.7356046605582289</v>
       </c>
       <c r="U24">
         <v>0.1468</v>
       </c>
       <c r="V24">
-        <v>0.172152760708619</v>
+        <v>0.1646678580691139</v>
       </c>
       <c r="W24">
-        <v>0.1215279747279747</v>
+        <v>0.1226267584354541</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.8607638035430951</v>
+        <v>0.8233392903455692</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09252923607122882</v>
+        <v>0.1068068574260488</v>
       </c>
       <c r="C25">
-        <v>31.60645040017056</v>
+        <v>19.68773323655574</v>
       </c>
       <c r="D25">
-        <v>47.60745040017056</v>
+        <v>36.46573323655575</v>
       </c>
       <c r="E25">
-        <v>5.971000000000002</v>
+        <v>6.748000000000003</v>
       </c>
       <c r="F25">
-        <v>17.871</v>
+        <v>18.648</v>
       </c>
       <c r="G25">
         <v>1.87</v>
@@ -3471,45 +3471,45 @@
         <v>2.16</v>
       </c>
       <c r="M25">
-        <v>2.6234628</v>
+        <v>3.744518400000001</v>
       </c>
       <c r="N25">
-        <v>-0.4634628000000003</v>
+        <v>-1.584518400000001</v>
       </c>
       <c r="O25">
-        <v>-0.09269256000000006</v>
+        <v>-0.3169036800000002</v>
       </c>
       <c r="P25">
-        <v>-0.3707702400000003</v>
+        <v>-1.267614720000001</v>
       </c>
       <c r="Q25">
-        <v>0.8292297599999995</v>
+        <v>-0.06761472000000079</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08353906705334334</v>
+        <v>0.08444039866565051</v>
       </c>
       <c r="T25">
-        <v>0.7356046605582289</v>
+        <v>0.7531732913297434</v>
       </c>
       <c r="U25">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1646678580691139</v>
+        <v>0.1153686412650556</v>
       </c>
       <c r="W25">
-        <v>0.1226267584354541</v>
+        <v>0.1776339768339768</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.8233392903455692</v>
+        <v>0.576843206325278</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1068068574260488</v>
+        <v>0.1083568574260488</v>
       </c>
       <c r="C26">
-        <v>19.68773323655575</v>
+        <v>18.00720500891935</v>
       </c>
       <c r="D26">
-        <v>36.46573323655576</v>
+        <v>35.56220500891935</v>
       </c>
       <c r="E26">
-        <v>6.747999999999999</v>
+        <v>7.525</v>
       </c>
       <c r="F26">
-        <v>18.648</v>
+        <v>19.425</v>
       </c>
       <c r="G26">
         <v>1.87</v>
@@ -3553,37 +3553,37 @@
         <v>2.16</v>
       </c>
       <c r="M26">
-        <v>3.7445184</v>
+        <v>3.90054</v>
       </c>
       <c r="N26">
-        <v>-1.5845184</v>
+        <v>-1.74054</v>
       </c>
       <c r="O26">
-        <v>-0.31690368</v>
+        <v>-0.3481080000000001</v>
       </c>
       <c r="P26">
-        <v>-1.26761472</v>
+        <v>-1.392432</v>
       </c>
       <c r="Q26">
-        <v>-0.06761472000000013</v>
+        <v>-0.1924320000000004</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08444039866565051</v>
+        <v>0.08495560398119251</v>
       </c>
       <c r="T26">
-        <v>0.7531732913297434</v>
+        <v>0.7632156018808066</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1153686412650556</v>
+        <v>0.1107538956144534</v>
       </c>
       <c r="W26">
-        <v>0.1776339768339768</v>
+        <v>0.1785606177606178</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5768432063252781</v>
+        <v>0.5537694780722668</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1083568574260488</v>
+        <v>0.1099068574260488</v>
       </c>
       <c r="C27">
-        <v>18.00720500891935</v>
+        <v>16.37036848008291</v>
       </c>
       <c r="D27">
-        <v>35.56220500891935</v>
+        <v>34.70236848008291</v>
       </c>
       <c r="E27">
-        <v>7.525</v>
+        <v>8.302000000000001</v>
       </c>
       <c r="F27">
-        <v>19.425</v>
+        <v>20.202</v>
       </c>
       <c r="G27">
         <v>1.87</v>
@@ -3635,37 +3635,37 @@
         <v>2.16</v>
       </c>
       <c r="M27">
-        <v>3.90054</v>
+        <v>4.0565616</v>
       </c>
       <c r="N27">
-        <v>-1.74054</v>
+        <v>-1.8965616</v>
       </c>
       <c r="O27">
-        <v>-0.3481080000000001</v>
+        <v>-0.37931232</v>
       </c>
       <c r="P27">
-        <v>-1.392432</v>
+        <v>-1.51724928</v>
       </c>
       <c r="Q27">
-        <v>-0.1924320000000004</v>
+        <v>-0.3172492800000004</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08495560398119251</v>
+        <v>0.08548473376472215</v>
       </c>
       <c r="T27">
-        <v>0.7632156018808066</v>
+        <v>0.7735293262305473</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1107538956144534</v>
+        <v>0.1064941303985129</v>
       </c>
       <c r="W27">
-        <v>0.1785606177606178</v>
+        <v>0.1794159786159786</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5537694780722668</v>
+        <v>0.5324706519925644</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1099068574260488</v>
+        <v>0.1114568574260488</v>
       </c>
       <c r="C28">
-        <v>16.37036848008291</v>
+        <v>14.77412928325245</v>
       </c>
       <c r="D28">
-        <v>34.70236848008291</v>
+        <v>33.88312928325245</v>
       </c>
       <c r="E28">
-        <v>8.302000000000001</v>
+        <v>9.079000000000002</v>
       </c>
       <c r="F28">
-        <v>20.202</v>
+        <v>20.979</v>
       </c>
       <c r="G28">
         <v>1.87</v>
@@ -3717,37 +3717,37 @@
         <v>2.16</v>
       </c>
       <c r="M28">
-        <v>4.0565616</v>
+        <v>4.212583200000001</v>
       </c>
       <c r="N28">
-        <v>-1.8965616</v>
+        <v>-2.052583200000001</v>
       </c>
       <c r="O28">
-        <v>-0.37931232</v>
+        <v>-0.4105166400000002</v>
       </c>
       <c r="P28">
-        <v>-1.51724928</v>
+        <v>-1.642066560000001</v>
       </c>
       <c r="Q28">
-        <v>-0.3172492800000004</v>
+        <v>-0.4420665600000009</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08548473376472215</v>
+        <v>0.08602836025464985</v>
       </c>
       <c r="T28">
-        <v>0.7735293262305473</v>
+        <v>0.7841256183706918</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.1064941303985129</v>
+        <v>0.1025499033467161</v>
       </c>
       <c r="W28">
-        <v>0.1794159786159786</v>
+        <v>0.1802079794079794</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.5324706519925644</v>
+        <v>0.5127495167335804</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1114568574260488</v>
+        <v>0.1229309863583726</v>
       </c>
       <c r="C29">
-        <v>14.77412928325245</v>
+        <v>8.956620761550752</v>
       </c>
       <c r="D29">
-        <v>33.88312928325245</v>
+        <v>28.84262076155076</v>
       </c>
       <c r="E29">
-        <v>9.079000000000002</v>
+        <v>9.856000000000003</v>
       </c>
       <c r="F29">
-        <v>20.979</v>
+        <v>21.756</v>
       </c>
       <c r="G29">
         <v>1.87</v>
@@ -3799,45 +3799,45 @@
         <v>2.16</v>
       </c>
       <c r="M29">
-        <v>4.212583200000001</v>
+        <v>5.130064800000001</v>
       </c>
       <c r="N29">
-        <v>-2.052583200000001</v>
+        <v>-2.970064800000001</v>
       </c>
       <c r="O29">
-        <v>-0.4105166400000002</v>
+        <v>-0.5940129600000003</v>
       </c>
       <c r="P29">
-        <v>-1.642066560000001</v>
+        <v>-2.376051840000001</v>
       </c>
       <c r="Q29">
-        <v>-0.4420665600000009</v>
+        <v>-1.176051840000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08602836025464985</v>
+        <v>0.08675948877530303</v>
       </c>
       <c r="T29">
-        <v>0.7841256183706918</v>
+        <v>0.7983766740870221</v>
       </c>
       <c r="U29">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.1025499033467161</v>
+        <v>0.0842094626173143</v>
       </c>
       <c r="W29">
-        <v>0.1802079794079794</v>
+        <v>0.2159434087148373</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.5127495167335804</v>
+        <v>0.4210473130865715</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1229309863583726</v>
+        <v>0.1248309863583726</v>
       </c>
       <c r="C30">
-        <v>8.956620761550752</v>
+        <v>7.48620945578207</v>
       </c>
       <c r="D30">
-        <v>28.84262076155076</v>
+        <v>28.14920945578207</v>
       </c>
       <c r="E30">
-        <v>9.856000000000003</v>
+        <v>10.633</v>
       </c>
       <c r="F30">
-        <v>21.756</v>
+        <v>22.533</v>
       </c>
       <c r="G30">
         <v>1.87</v>
@@ -3881,37 +3881,37 @@
         <v>2.16</v>
       </c>
       <c r="M30">
-        <v>5.130064800000001</v>
+        <v>5.313281400000001</v>
       </c>
       <c r="N30">
-        <v>-2.970064800000001</v>
+        <v>-3.153281400000001</v>
       </c>
       <c r="O30">
-        <v>-0.5940129600000003</v>
+        <v>-0.6306562800000002</v>
       </c>
       <c r="P30">
-        <v>-2.376051840000001</v>
+        <v>-2.522625120000001</v>
       </c>
       <c r="Q30">
-        <v>-1.176051840000001</v>
+        <v>-1.322625120000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08675948877530303</v>
+        <v>0.08733638298340587</v>
       </c>
       <c r="T30">
-        <v>0.7983766740870221</v>
+        <v>0.8096214159755717</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.0842094626173143</v>
+        <v>0.08130568804430346</v>
       </c>
       <c r="W30">
-        <v>0.2159434087148373</v>
+        <v>0.2166281187591532</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4210473130865715</v>
+        <v>0.4065284402215172</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1248309863583726</v>
+        <v>0.1267309863583726</v>
       </c>
       <c r="C31">
-        <v>7.486209455782085</v>
+        <v>6.048356297151908</v>
       </c>
       <c r="D31">
-        <v>28.14920945578208</v>
+        <v>27.48835629715191</v>
       </c>
       <c r="E31">
-        <v>10.633</v>
+        <v>11.41</v>
       </c>
       <c r="F31">
-        <v>22.533</v>
+        <v>23.31</v>
       </c>
       <c r="G31">
         <v>1.87</v>
@@ -3963,37 +3963,37 @@
         <v>2.16</v>
       </c>
       <c r="M31">
-        <v>5.313281399999999</v>
+        <v>5.496498</v>
       </c>
       <c r="N31">
-        <v>-3.153281399999999</v>
+        <v>-3.336498</v>
       </c>
       <c r="O31">
-        <v>-0.6306562799999998</v>
+        <v>-0.6672996</v>
       </c>
       <c r="P31">
-        <v>-2.522625119999999</v>
+        <v>-2.6691984</v>
       </c>
       <c r="Q31">
-        <v>-1.32262512</v>
+        <v>-1.4691984</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08733638298340587</v>
+        <v>0.08792975988316881</v>
       </c>
       <c r="T31">
-        <v>0.8096214159755716</v>
+        <v>0.821187436203794</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.08130568804430349</v>
+        <v>0.07859549844282671</v>
       </c>
       <c r="W31">
-        <v>0.2166281187591532</v>
+        <v>0.2172671814671815</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.4065284402215175</v>
+        <v>0.3929774922141335</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1267309863583726</v>
+        <v>0.1286309863583726</v>
       </c>
       <c r="C32">
-        <v>6.048356297151908</v>
+        <v>4.640820802396089</v>
       </c>
       <c r="D32">
-        <v>27.48835629715191</v>
+        <v>26.85782080239609</v>
       </c>
       <c r="E32">
-        <v>11.41</v>
+        <v>12.187</v>
       </c>
       <c r="F32">
-        <v>23.31</v>
+        <v>24.087</v>
       </c>
       <c r="G32">
         <v>1.87</v>
@@ -4045,37 +4045,37 @@
         <v>2.16</v>
       </c>
       <c r="M32">
-        <v>5.496498</v>
+        <v>5.679714600000001</v>
       </c>
       <c r="N32">
-        <v>-3.336498</v>
+        <v>-3.5197146</v>
       </c>
       <c r="O32">
-        <v>-0.6672996</v>
+        <v>-0.7039429200000001</v>
       </c>
       <c r="P32">
-        <v>-2.6691984</v>
+        <v>-2.81577168</v>
       </c>
       <c r="Q32">
-        <v>-1.4691984</v>
+        <v>-1.61577168</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08792975988316881</v>
+        <v>0.08854033611335967</v>
       </c>
       <c r="T32">
-        <v>0.821187436203794</v>
+        <v>0.8330887033951533</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.07859549844282671</v>
+        <v>0.07606015978338067</v>
       </c>
       <c r="W32">
-        <v>0.2172671814671815</v>
+        <v>0.2178650143230788</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3929774922141335</v>
+        <v>0.3803007989169033</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1286309863583726</v>
+        <v>0.1305309863583726</v>
       </c>
       <c r="C33">
-        <v>4.640820802396089</v>
+        <v>3.261563449829449</v>
       </c>
       <c r="D33">
-        <v>26.85782080239609</v>
+        <v>26.25556344982945</v>
       </c>
       <c r="E33">
-        <v>12.187</v>
+        <v>12.964</v>
       </c>
       <c r="F33">
-        <v>24.087</v>
+        <v>24.864</v>
       </c>
       <c r="G33">
         <v>1.87</v>
@@ -4127,37 +4127,37 @@
         <v>2.16</v>
       </c>
       <c r="M33">
-        <v>5.679714600000001</v>
+        <v>5.8629312</v>
       </c>
       <c r="N33">
-        <v>-3.5197146</v>
+        <v>-3.7029312</v>
       </c>
       <c r="O33">
-        <v>-0.7039429200000001</v>
+        <v>-0.7405862400000001</v>
       </c>
       <c r="P33">
-        <v>-2.81577168</v>
+        <v>-2.96234496</v>
       </c>
       <c r="Q33">
-        <v>-1.61577168</v>
+        <v>-1.762344960000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08854033611335967</v>
+        <v>0.08916887046796791</v>
       </c>
       <c r="T33">
-        <v>0.8330887033951533</v>
+        <v>0.8453400078568469</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.07606015978338067</v>
+        <v>0.07368327979015003</v>
       </c>
       <c r="W33">
-        <v>0.2178650143230788</v>
+        <v>0.2184254826254826</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3803007989169033</v>
+        <v>0.3684163989507501</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1305309863583726</v>
+        <v>0.1324309863583726</v>
       </c>
       <c r="C34">
-        <v>3.261563449829449</v>
+        <v>1.908723641792282</v>
       </c>
       <c r="D34">
-        <v>26.25556344982945</v>
+        <v>25.67972364179228</v>
       </c>
       <c r="E34">
-        <v>12.964</v>
+        <v>13.741</v>
       </c>
       <c r="F34">
-        <v>24.864</v>
+        <v>25.641</v>
       </c>
       <c r="G34">
         <v>1.87</v>
@@ -4209,37 +4209,37 @@
         <v>2.16</v>
       </c>
       <c r="M34">
-        <v>5.8629312</v>
+        <v>6.046147800000001</v>
       </c>
       <c r="N34">
-        <v>-3.7029312</v>
+        <v>-3.886147800000001</v>
       </c>
       <c r="O34">
-        <v>-0.7405862400000001</v>
+        <v>-0.7772295600000002</v>
       </c>
       <c r="P34">
-        <v>-2.96234496</v>
+        <v>-3.10891824</v>
       </c>
       <c r="Q34">
-        <v>-1.762344960000001</v>
+        <v>-1.908918240000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08916887046796791</v>
+        <v>0.08981616704211669</v>
       </c>
       <c r="T34">
-        <v>0.8453400078568469</v>
+        <v>0.8579570228994865</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.07368327979015003</v>
+        <v>0.07145045312984244</v>
       </c>
       <c r="W34">
-        <v>0.2184254826254826</v>
+        <v>0.2189519831519832</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3684163989507501</v>
+        <v>0.3572522656492122</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1324309863583726</v>
+        <v>0.1343309863583726</v>
       </c>
       <c r="C35">
-        <v>1.908723641792282</v>
+        <v>0.5806005048388805</v>
       </c>
       <c r="D35">
-        <v>25.67972364179228</v>
+        <v>25.12860050483888</v>
       </c>
       <c r="E35">
-        <v>13.741</v>
+        <v>14.518</v>
       </c>
       <c r="F35">
-        <v>25.641</v>
+        <v>26.418</v>
       </c>
       <c r="G35">
         <v>1.87</v>
@@ -4291,37 +4291,37 @@
         <v>2.16</v>
       </c>
       <c r="M35">
-        <v>6.046147800000001</v>
+        <v>6.229364400000001</v>
       </c>
       <c r="N35">
-        <v>-3.886147800000001</v>
+        <v>-4.0693644</v>
       </c>
       <c r="O35">
-        <v>-0.7772295600000002</v>
+        <v>-0.8138728800000001</v>
       </c>
       <c r="P35">
-        <v>-3.10891824</v>
+        <v>-3.255491520000001</v>
       </c>
       <c r="Q35">
-        <v>-1.908918240000001</v>
+        <v>-2.055491520000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08981616704211669</v>
+        <v>0.09048307866396693</v>
       </c>
       <c r="T35">
-        <v>0.8579570228994865</v>
+        <v>0.8709563717312968</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07145045312984244</v>
+        <v>0.06934896921425884</v>
       </c>
       <c r="W35">
-        <v>0.2189519831519832</v>
+        <v>0.2194475130592778</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3572522656492122</v>
+        <v>0.3467448460712942</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1343309863583726</v>
+        <v>0.1362309863583726</v>
       </c>
       <c r="C36">
-        <v>0.5806005048388805</v>
+        <v>-0.7243638896882985</v>
       </c>
       <c r="D36">
-        <v>25.12860050483888</v>
+        <v>24.6006361103117</v>
       </c>
       <c r="E36">
-        <v>14.518</v>
+        <v>15.295</v>
       </c>
       <c r="F36">
-        <v>26.418</v>
+        <v>27.195</v>
       </c>
       <c r="G36">
         <v>1.87</v>
@@ -4373,37 +4373,37 @@
         <v>2.16</v>
       </c>
       <c r="M36">
-        <v>6.229364400000001</v>
+        <v>6.412581000000001</v>
       </c>
       <c r="N36">
-        <v>-4.0693644</v>
+        <v>-4.252581000000001</v>
       </c>
       <c r="O36">
-        <v>-0.8138728800000001</v>
+        <v>-0.8505162000000003</v>
       </c>
       <c r="P36">
-        <v>-3.255491520000001</v>
+        <v>-3.402064800000001</v>
       </c>
       <c r="Q36">
-        <v>-2.055491520000001</v>
+        <v>-2.202064800000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09048307866396693</v>
+        <v>0.09117051064341258</v>
       </c>
       <c r="T36">
-        <v>0.8709563717312968</v>
+        <v>0.8843557005271629</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.06934896921425884</v>
+        <v>0.06736757009385144</v>
       </c>
       <c r="W36">
-        <v>0.2194475130592778</v>
+        <v>0.2199147269718698</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3467448460712942</v>
+        <v>0.3368378504692572</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1362309863583726</v>
+        <v>0.1381309863583726</v>
       </c>
       <c r="C37">
-        <v>-0.7243638896882985</v>
+        <v>-2.007599233348248</v>
       </c>
       <c r="D37">
-        <v>24.6006361103117</v>
+        <v>24.09440076665176</v>
       </c>
       <c r="E37">
-        <v>15.295</v>
+        <v>16.072</v>
       </c>
       <c r="F37">
-        <v>27.195</v>
+        <v>27.972</v>
       </c>
       <c r="G37">
         <v>1.87</v>
@@ -4455,37 +4455,37 @@
         <v>2.16</v>
       </c>
       <c r="M37">
-        <v>6.412581000000001</v>
+        <v>6.595797600000002</v>
       </c>
       <c r="N37">
-        <v>-4.252581000000001</v>
+        <v>-4.435797600000002</v>
       </c>
       <c r="O37">
-        <v>-0.8505162000000003</v>
+        <v>-0.8871595200000004</v>
       </c>
       <c r="P37">
-        <v>-3.402064800000001</v>
+        <v>-3.548638080000001</v>
       </c>
       <c r="Q37">
-        <v>-2.202064800000001</v>
+        <v>-2.348638080000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09117051064341258</v>
+        <v>0.0918794248722159</v>
       </c>
       <c r="T37">
-        <v>0.8843557005271629</v>
+        <v>0.8981737583478997</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.06736757009385144</v>
+        <v>0.06549624870235557</v>
       </c>
       <c r="W37">
-        <v>0.2199147269718698</v>
+        <v>0.2203559845559846</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3368378504692572</v>
+        <v>0.3274812435117778</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1381309863583726</v>
+        <v>0.1400309863583726</v>
       </c>
       <c r="C38">
-        <v>-2.007599233348245</v>
+        <v>-3.27041990896479</v>
       </c>
       <c r="D38">
-        <v>24.09440076665176</v>
+        <v>23.60858009103521</v>
       </c>
       <c r="E38">
-        <v>16.072</v>
+        <v>16.849</v>
       </c>
       <c r="F38">
-        <v>27.972</v>
+        <v>28.749</v>
       </c>
       <c r="G38">
         <v>1.87</v>
@@ -4537,37 +4537,37 @@
         <v>2.16</v>
       </c>
       <c r="M38">
-        <v>6.595797600000001</v>
+        <v>6.779014200000001</v>
       </c>
       <c r="N38">
-        <v>-4.435797600000001</v>
+        <v>-4.619014200000001</v>
       </c>
       <c r="O38">
-        <v>-0.8871595200000002</v>
+        <v>-0.9238028400000001</v>
       </c>
       <c r="P38">
-        <v>-3.548638080000001</v>
+        <v>-3.695211360000001</v>
       </c>
       <c r="Q38">
-        <v>-2.348638080000001</v>
+        <v>-2.495211360000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0918794248722159</v>
+        <v>0.09261084431463201</v>
       </c>
       <c r="T38">
-        <v>0.8981737583478997</v>
+        <v>0.9124304846708823</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.06549624870235557</v>
+        <v>0.06372607981850813</v>
       </c>
       <c r="W38">
-        <v>0.2203559845559846</v>
+        <v>0.2207733903787958</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3274812435117779</v>
+        <v>0.3186303990925407</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1400309863583726</v>
+        <v>0.1419309863583726</v>
       </c>
       <c r="C39">
-        <v>-3.27041990896479</v>
+        <v>-4.514036385838793</v>
       </c>
       <c r="D39">
-        <v>23.60858009103521</v>
+        <v>23.14196361416121</v>
       </c>
       <c r="E39">
-        <v>16.849</v>
+        <v>17.626</v>
       </c>
       <c r="F39">
-        <v>28.749</v>
+        <v>29.526</v>
       </c>
       <c r="G39">
         <v>1.87</v>
@@ -4619,37 +4619,37 @@
         <v>2.16</v>
       </c>
       <c r="M39">
-        <v>6.779014200000001</v>
+        <v>6.9622308</v>
       </c>
       <c r="N39">
-        <v>-4.619014200000001</v>
+        <v>-4.8022308</v>
       </c>
       <c r="O39">
-        <v>-0.9238028400000001</v>
+        <v>-0.96044616</v>
       </c>
       <c r="P39">
-        <v>-3.695211360000001</v>
+        <v>-3.84178464</v>
       </c>
       <c r="Q39">
-        <v>-2.495211360000001</v>
+        <v>-2.64178464</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09261084431463201</v>
+        <v>0.09336585793260996</v>
       </c>
       <c r="T39">
-        <v>0.9124304846708823</v>
+        <v>0.9271471053913805</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.06372607981850813</v>
+        <v>0.06204907771802107</v>
       </c>
       <c r="W39">
-        <v>0.2207733903787958</v>
+        <v>0.2211688274740906</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3186303990925407</v>
+        <v>0.3102453885901053</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1419309863583726</v>
+        <v>0.1438309863583726</v>
       </c>
       <c r="C40">
-        <v>-4.514036385838793</v>
+        <v>-5.739565289813768</v>
       </c>
       <c r="D40">
-        <v>23.14196361416121</v>
+        <v>22.69343471018623</v>
       </c>
       <c r="E40">
-        <v>17.626</v>
+        <v>18.403</v>
       </c>
       <c r="F40">
-        <v>29.526</v>
+        <v>30.303</v>
       </c>
       <c r="G40">
         <v>1.87</v>
@@ -4701,37 +4701,37 @@
         <v>2.16</v>
       </c>
       <c r="M40">
-        <v>6.9622308</v>
+        <v>7.1454474</v>
       </c>
       <c r="N40">
-        <v>-4.8022308</v>
+        <v>-4.9854474</v>
       </c>
       <c r="O40">
-        <v>-0.96044616</v>
+        <v>-0.9970894800000001</v>
       </c>
       <c r="P40">
-        <v>-3.84178464</v>
+        <v>-3.98835792</v>
       </c>
       <c r="Q40">
-        <v>-2.64178464</v>
+        <v>-2.78835792</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09336585793260996</v>
+        <v>0.09414562609543964</v>
       </c>
       <c r="T40">
-        <v>0.9271471053913805</v>
+        <v>0.942346238266649</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06204907771802107</v>
+        <v>0.0604580757252513</v>
       </c>
       <c r="W40">
-        <v>0.2211688274740906</v>
+        <v>0.2215439857439858</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3102453885901053</v>
+        <v>0.3022903786262565</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1438309863583726</v>
+        <v>0.1457309863583726</v>
       </c>
       <c r="C41">
-        <v>-5.739565289813768</v>
+        <v>-6.948038324561228</v>
       </c>
       <c r="D41">
-        <v>22.69343471018623</v>
+        <v>22.26196167543877</v>
       </c>
       <c r="E41">
-        <v>18.403</v>
+        <v>19.18</v>
       </c>
       <c r="F41">
-        <v>30.303</v>
+        <v>31.08</v>
       </c>
       <c r="G41">
         <v>1.87</v>
@@ -4783,37 +4783,37 @@
         <v>2.16</v>
       </c>
       <c r="M41">
-        <v>7.1454474</v>
+        <v>7.328664000000001</v>
       </c>
       <c r="N41">
-        <v>-4.9854474</v>
+        <v>-5.168664000000001</v>
       </c>
       <c r="O41">
-        <v>-0.9970894800000001</v>
+        <v>-1.0337328</v>
       </c>
       <c r="P41">
-        <v>-3.98835792</v>
+        <v>-4.1349312</v>
       </c>
       <c r="Q41">
-        <v>-2.78835792</v>
+        <v>-2.934931200000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09414562609543964</v>
+        <v>0.09495138653036361</v>
       </c>
       <c r="T41">
-        <v>0.942346238266649</v>
+        <v>0.9580520089044263</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.0604580757252513</v>
+        <v>0.05894662383212002</v>
       </c>
       <c r="W41">
-        <v>0.2215439857439858</v>
+        <v>0.2219003861003861</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3022903786262565</v>
+        <v>0.2947331191606001</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1457309863583726</v>
+        <v>0.1476309863583726</v>
       </c>
       <c r="C42">
-        <v>-6.948038324561228</v>
+        <v>-8.140410194126311</v>
       </c>
       <c r="D42">
-        <v>22.26196167543877</v>
+        <v>21.84658980587369</v>
       </c>
       <c r="E42">
-        <v>19.18</v>
+        <v>19.957</v>
       </c>
       <c r="F42">
-        <v>31.08</v>
+        <v>31.857</v>
       </c>
       <c r="G42">
         <v>1.87</v>
@@ -4865,37 +4865,37 @@
         <v>2.16</v>
       </c>
       <c r="M42">
-        <v>7.328664000000001</v>
+        <v>7.511880600000001</v>
       </c>
       <c r="N42">
-        <v>-5.168664000000001</v>
+        <v>-5.351880600000001</v>
       </c>
       <c r="O42">
-        <v>-1.0337328</v>
+        <v>-1.07037612</v>
       </c>
       <c r="P42">
-        <v>-4.1349312</v>
+        <v>-4.281504480000001</v>
       </c>
       <c r="Q42">
-        <v>-2.934931200000001</v>
+        <v>-3.081504480000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09495138653036361</v>
+        <v>0.09578446087833589</v>
       </c>
       <c r="T42">
-        <v>0.9580520089044263</v>
+        <v>0.9742901785468744</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05894662383212002</v>
+        <v>0.05750890129962928</v>
       </c>
       <c r="W42">
-        <v>0.2219003861003861</v>
+        <v>0.2222394010735474</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2947331191606001</v>
+        <v>0.2875445064981463</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1476309863583726</v>
+        <v>0.1495309863583726</v>
       </c>
       <c r="C43">
-        <v>-8.140410194126311</v>
+        <v>-9.317565654788336</v>
       </c>
       <c r="D43">
-        <v>21.84658980587369</v>
+        <v>21.44643434521167</v>
       </c>
       <c r="E43">
-        <v>19.957</v>
+        <v>20.73400000000001</v>
       </c>
       <c r="F43">
-        <v>31.857</v>
+        <v>32.63400000000001</v>
       </c>
       <c r="G43">
         <v>1.87</v>
@@ -4947,37 +4947,37 @@
         <v>2.16</v>
       </c>
       <c r="M43">
-        <v>7.511880600000001</v>
+        <v>7.695097200000002</v>
       </c>
       <c r="N43">
-        <v>-5.351880600000001</v>
+        <v>-5.535097200000002</v>
       </c>
       <c r="O43">
-        <v>-1.07037612</v>
+        <v>-1.10701944</v>
       </c>
       <c r="P43">
-        <v>-4.281504480000001</v>
+        <v>-4.428077760000002</v>
       </c>
       <c r="Q43">
-        <v>-3.081504480000001</v>
+        <v>-3.228077760000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09578446087833589</v>
+        <v>0.09664626192796237</v>
       </c>
       <c r="T43">
-        <v>0.9742901785468744</v>
+        <v>0.9910882850735446</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.05750890129962928</v>
+        <v>0.05613964174487619</v>
       </c>
       <c r="W43">
-        <v>0.2222394010735474</v>
+        <v>0.2225622724765582</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2875445064981463</v>
+        <v>0.280698208724381</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1495309863583726</v>
+        <v>0.1514309863583726</v>
       </c>
       <c r="C44">
-        <v>-9.317565654788329</v>
+        <v>-10.48032580586422</v>
       </c>
       <c r="D44">
-        <v>21.44643434521167</v>
+        <v>21.06067419413578</v>
       </c>
       <c r="E44">
-        <v>20.734</v>
+        <v>21.511</v>
       </c>
       <c r="F44">
-        <v>32.634</v>
+        <v>33.411</v>
       </c>
       <c r="G44">
         <v>1.87</v>
@@ -5029,37 +5029,37 @@
         <v>2.16</v>
       </c>
       <c r="M44">
-        <v>7.6950972</v>
+        <v>7.878313800000001</v>
       </c>
       <c r="N44">
-        <v>-5.5350972</v>
+        <v>-5.718313800000001</v>
       </c>
       <c r="O44">
-        <v>-1.10701944</v>
+        <v>-1.14366276</v>
       </c>
       <c r="P44">
-        <v>-4.42807776</v>
+        <v>-4.574651040000001</v>
       </c>
       <c r="Q44">
-        <v>-3.22807776</v>
+        <v>-3.374651040000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09664626192796236</v>
+        <v>0.09753830161090907</v>
       </c>
       <c r="T44">
-        <v>0.9910882850735444</v>
+        <v>1.008475798846765</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05613964174487621</v>
+        <v>0.05483406868104188</v>
       </c>
       <c r="W44">
-        <v>0.2225622724765582</v>
+        <v>0.2228701266050103</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.280698208724381</v>
+        <v>0.2741703434052094</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1514309863583726</v>
+        <v>0.1533309863583726</v>
       </c>
       <c r="C45">
-        <v>-10.48032580586422</v>
+        <v>-11.62945371358654</v>
       </c>
       <c r="D45">
-        <v>21.06067419413578</v>
+        <v>20.68854628641346</v>
       </c>
       <c r="E45">
-        <v>21.511</v>
+        <v>22.288</v>
       </c>
       <c r="F45">
-        <v>33.411</v>
+        <v>34.188</v>
       </c>
       <c r="G45">
         <v>1.87</v>
@@ -5111,37 +5111,37 @@
         <v>2.16</v>
       </c>
       <c r="M45">
-        <v>7.878313800000001</v>
+        <v>8.061530400000001</v>
       </c>
       <c r="N45">
-        <v>-5.718313800000001</v>
+        <v>-5.9015304</v>
       </c>
       <c r="O45">
-        <v>-1.14366276</v>
+        <v>-1.18030608</v>
       </c>
       <c r="P45">
-        <v>-4.574651040000001</v>
+        <v>-4.72122432</v>
       </c>
       <c r="Q45">
-        <v>-3.374651040000001</v>
+        <v>-3.52122432</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09753830161090907</v>
+        <v>0.09846219985396103</v>
       </c>
       <c r="T45">
-        <v>1.008475798846765</v>
+        <v>1.026484295254743</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05483406868104188</v>
+        <v>0.05358783984738184</v>
       </c>
       <c r="W45">
-        <v>0.2228701266050103</v>
+        <v>0.2231639873639874</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2741703434052094</v>
+        <v>0.2679391992369091</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1533309863583726</v>
+        <v>0.1552309863583726</v>
       </c>
       <c r="C46">
-        <v>-11.62945371358654</v>
+        <v>-12.76565944911246</v>
       </c>
       <c r="D46">
-        <v>20.68854628641346</v>
+        <v>20.32934055088755</v>
       </c>
       <c r="E46">
-        <v>22.288</v>
+        <v>23.065</v>
       </c>
       <c r="F46">
-        <v>34.188</v>
+        <v>34.965</v>
       </c>
       <c r="G46">
         <v>1.87</v>
@@ -5193,37 +5193,37 @@
         <v>2.16</v>
       </c>
       <c r="M46">
-        <v>8.061530400000001</v>
+        <v>8.244747</v>
       </c>
       <c r="N46">
-        <v>-5.9015304</v>
+        <v>-6.084747</v>
       </c>
       <c r="O46">
-        <v>-1.18030608</v>
+        <v>-1.2169494</v>
       </c>
       <c r="P46">
-        <v>-4.72122432</v>
+        <v>-4.8677976</v>
       </c>
       <c r="Q46">
-        <v>-3.52122432</v>
+        <v>-3.667797600000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09846219985396103</v>
+        <v>0.09941969439676031</v>
       </c>
       <c r="T46">
-        <v>1.026484295254743</v>
+        <v>1.045147646077556</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05358783984738184</v>
+        <v>0.05239699896188446</v>
       </c>
       <c r="W46">
-        <v>0.2231639873639874</v>
+        <v>0.2234447876447877</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2679391992369091</v>
+        <v>0.2619849948094223</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1552309863583726</v>
+        <v>0.1571309863583726</v>
       </c>
       <c r="C47">
-        <v>-12.76565944911246</v>
+        <v>-13.88960461065402</v>
       </c>
       <c r="D47">
-        <v>20.32934055088755</v>
+        <v>19.98239538934599</v>
       </c>
       <c r="E47">
-        <v>23.065</v>
+        <v>23.84200000000001</v>
       </c>
       <c r="F47">
-        <v>34.965</v>
+        <v>35.742</v>
       </c>
       <c r="G47">
         <v>1.87</v>
@@ -5275,37 +5275,37 @@
         <v>2.16</v>
       </c>
       <c r="M47">
-        <v>8.244747</v>
+        <v>8.427963600000002</v>
       </c>
       <c r="N47">
-        <v>-6.084747</v>
+        <v>-6.267963600000002</v>
       </c>
       <c r="O47">
-        <v>-1.2169494</v>
+        <v>-1.25359272</v>
       </c>
       <c r="P47">
-        <v>-4.8677976</v>
+        <v>-5.014370880000001</v>
       </c>
       <c r="Q47">
-        <v>-3.667797600000001</v>
+        <v>-3.814370880000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09941969439676031</v>
+        <v>0.100412651700404</v>
       </c>
       <c r="T47">
-        <v>1.045147646077556</v>
+        <v>1.064502232116029</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05239699896188446</v>
+        <v>0.05125793376706087</v>
       </c>
       <c r="W47">
-        <v>0.2234447876447877</v>
+        <v>0.223713379217727</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2619849948094223</v>
+        <v>0.2562896688353044</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1571309863583726</v>
+        <v>0.1590309863583727</v>
       </c>
       <c r="C48">
-        <v>-13.88960461065402</v>
+        <v>-15.00190639032407</v>
       </c>
       <c r="D48">
-        <v>19.98239538934599</v>
+        <v>19.64709360967594</v>
       </c>
       <c r="E48">
-        <v>23.84200000000001</v>
+        <v>24.61900000000001</v>
       </c>
       <c r="F48">
-        <v>35.742</v>
+        <v>36.51900000000001</v>
       </c>
       <c r="G48">
         <v>1.87</v>
@@ -5357,37 +5357,37 @@
         <v>2.16</v>
       </c>
       <c r="M48">
-        <v>8.427963600000002</v>
+        <v>8.611180200000002</v>
       </c>
       <c r="N48">
-        <v>-6.267963600000002</v>
+        <v>-6.451180200000001</v>
       </c>
       <c r="O48">
-        <v>-1.25359272</v>
+        <v>-1.29023604</v>
       </c>
       <c r="P48">
-        <v>-5.014370880000001</v>
+        <v>-5.160944160000001</v>
       </c>
       <c r="Q48">
-        <v>-3.814370880000002</v>
+        <v>-3.960944160000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.100412651700404</v>
+        <v>0.1014430790909777</v>
       </c>
       <c r="T48">
-        <v>1.064502232116029</v>
+        <v>1.084587179891804</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05125793376706087</v>
+        <v>0.0501673394315915</v>
       </c>
       <c r="W48">
-        <v>0.223713379217727</v>
+        <v>0.2239705413620307</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2562896688353044</v>
+        <v>0.2508366971579575</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1590309863583727</v>
+        <v>0.1609309863583726</v>
       </c>
       <c r="C49">
-        <v>-15.00190639032407</v>
+        <v>-16.10314123829269</v>
       </c>
       <c r="D49">
-        <v>19.64709360967594</v>
+        <v>19.32285876170732</v>
       </c>
       <c r="E49">
-        <v>24.61900000000001</v>
+        <v>25.39600000000001</v>
       </c>
       <c r="F49">
-        <v>36.51900000000001</v>
+        <v>37.29600000000001</v>
       </c>
       <c r="G49">
         <v>1.87</v>
@@ -5439,37 +5439,37 @@
         <v>2.16</v>
       </c>
       <c r="M49">
-        <v>8.611180200000002</v>
+        <v>8.794396800000001</v>
       </c>
       <c r="N49">
-        <v>-6.451180200000001</v>
+        <v>-6.634396800000001</v>
       </c>
       <c r="O49">
-        <v>-1.29023604</v>
+        <v>-1.32687936</v>
       </c>
       <c r="P49">
-        <v>-5.160944160000001</v>
+        <v>-5.307517440000001</v>
       </c>
       <c r="Q49">
-        <v>-3.960944160000002</v>
+        <v>-4.107517440000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1014430790909777</v>
+        <v>0.1025131383042657</v>
       </c>
       <c r="T49">
-        <v>1.084587179891804</v>
+        <v>1.105444625658953</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0501673394315915</v>
+        <v>0.04912218652676668</v>
       </c>
       <c r="W49">
-        <v>0.2239705413620307</v>
+        <v>0.2242169884169884</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2508366971579575</v>
+        <v>0.2456109326338334</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1609309863583726</v>
+        <v>0.1628309863583726</v>
       </c>
       <c r="C50">
-        <v>-16.10314123829268</v>
+        <v>-17.19384817001775</v>
       </c>
       <c r="D50">
-        <v>19.32285876170732</v>
+        <v>19.00915182998225</v>
       </c>
       <c r="E50">
-        <v>25.396</v>
+        <v>26.173</v>
       </c>
       <c r="F50">
-        <v>37.296</v>
+        <v>38.073</v>
       </c>
       <c r="G50">
         <v>1.87</v>
@@ -5521,37 +5521,37 @@
         <v>2.16</v>
       </c>
       <c r="M50">
-        <v>8.794396799999999</v>
+        <v>8.977613400000001</v>
       </c>
       <c r="N50">
-        <v>-6.634396799999999</v>
+        <v>-6.817613400000001</v>
       </c>
       <c r="O50">
-        <v>-1.32687936</v>
+        <v>-1.36352268</v>
       </c>
       <c r="P50">
-        <v>-5.30751744</v>
+        <v>-5.454090720000001</v>
       </c>
       <c r="Q50">
-        <v>-4.107517440000001</v>
+        <v>-4.254090720000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1025131383042657</v>
+        <v>0.1036251606239572</v>
       </c>
       <c r="T50">
-        <v>1.105444625658953</v>
+        <v>1.127120010475796</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04912218652676669</v>
+        <v>0.04811969292417961</v>
       </c>
       <c r="W50">
-        <v>0.2242169884169884</v>
+        <v>0.2244533764084785</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2456109326338334</v>
+        <v>0.2405984646208981</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1628309863583726</v>
+        <v>0.1647309863583726</v>
       </c>
       <c r="C51">
-        <v>-17.19384817001775</v>
+        <v>-18.27453175646456</v>
       </c>
       <c r="D51">
-        <v>19.00915182998225</v>
+        <v>18.70546824353544</v>
       </c>
       <c r="E51">
-        <v>26.173</v>
+        <v>26.95</v>
       </c>
       <c r="F51">
-        <v>38.073</v>
+        <v>38.85</v>
       </c>
       <c r="G51">
         <v>1.87</v>
@@ -5603,37 +5603,37 @@
         <v>2.16</v>
       </c>
       <c r="M51">
-        <v>8.977613400000001</v>
+        <v>9.160830000000001</v>
       </c>
       <c r="N51">
-        <v>-6.817613400000001</v>
+        <v>-7.000830000000001</v>
       </c>
       <c r="O51">
-        <v>-1.36352268</v>
+        <v>-1.400166</v>
       </c>
       <c r="P51">
-        <v>-5.454090720000001</v>
+        <v>-5.600664</v>
       </c>
       <c r="Q51">
-        <v>-4.254090720000001</v>
+        <v>-4.400664000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1036251606239572</v>
+        <v>0.1047816638364363</v>
       </c>
       <c r="T51">
-        <v>1.127120010475796</v>
+        <v>1.149662410685312</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04811969292417961</v>
+        <v>0.04715729906569602</v>
       </c>
       <c r="W51">
-        <v>0.2244533764084785</v>
+        <v>0.2246803088803089</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2405984646208981</v>
+        <v>0.2357864953284801</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1647309863583726</v>
+        <v>0.1666309863583726</v>
       </c>
       <c r="C52">
-        <v>-18.27453175646456</v>
+        <v>-19.34566483220812</v>
       </c>
       <c r="D52">
-        <v>18.70546824353544</v>
+        <v>18.41133516779188</v>
       </c>
       <c r="E52">
-        <v>26.95</v>
+        <v>27.727</v>
       </c>
       <c r="F52">
-        <v>38.85</v>
+        <v>39.627</v>
       </c>
       <c r="G52">
         <v>1.87</v>
@@ -5685,37 +5685,37 @@
         <v>2.16</v>
       </c>
       <c r="M52">
-        <v>9.160830000000001</v>
+        <v>9.3440466</v>
       </c>
       <c r="N52">
-        <v>-7.000830000000001</v>
+        <v>-7.1840466</v>
       </c>
       <c r="O52">
-        <v>-1.400166</v>
+        <v>-1.43680932</v>
       </c>
       <c r="P52">
-        <v>-5.600664</v>
+        <v>-5.74723728</v>
       </c>
       <c r="Q52">
-        <v>-4.400664000000001</v>
+        <v>-4.547237280000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1047816638364363</v>
+        <v>0.1059853712616698</v>
       </c>
       <c r="T52">
-        <v>1.149662410685312</v>
+        <v>1.173124908862563</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04715729906569602</v>
+        <v>0.04623264614283923</v>
       </c>
       <c r="W52">
-        <v>0.2246803088803089</v>
+        <v>0.2248983420395185</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2357864953284801</v>
+        <v>0.2311632307141961</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1666309863583726</v>
+        <v>0.1685309863583726</v>
       </c>
       <c r="C53">
-        <v>-19.34566483220812</v>
+        <v>-20.40769095199062</v>
       </c>
       <c r="D53">
-        <v>18.41133516779188</v>
+        <v>18.12630904800938</v>
       </c>
       <c r="E53">
-        <v>27.727</v>
+        <v>28.504</v>
       </c>
       <c r="F53">
-        <v>39.627</v>
+        <v>40.404</v>
       </c>
       <c r="G53">
         <v>1.87</v>
@@ -5767,37 +5767,37 @@
         <v>2.16</v>
       </c>
       <c r="M53">
-        <v>9.3440466</v>
+        <v>9.527263200000002</v>
       </c>
       <c r="N53">
-        <v>-7.1840466</v>
+        <v>-7.367263200000002</v>
       </c>
       <c r="O53">
-        <v>-1.43680932</v>
+        <v>-1.473452640000001</v>
       </c>
       <c r="P53">
-        <v>-5.74723728</v>
+        <v>-5.893810560000001</v>
       </c>
       <c r="Q53">
-        <v>-4.547237280000001</v>
+        <v>-4.693810560000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1059853712616698</v>
+        <v>0.1072392331629545</v>
       </c>
       <c r="T53">
-        <v>1.173124908862563</v>
+        <v>1.197565011130533</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04623264614283923</v>
+        <v>0.04534355679393847</v>
       </c>
       <c r="W53">
-        <v>0.2248983420395185</v>
+        <v>0.2251079893079893</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2311632307141961</v>
+        <v>0.2267177839696923</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1685309863583726</v>
+        <v>0.1704309863583726</v>
       </c>
       <c r="C54">
-        <v>-20.40769095199062</v>
+        <v>-21.46102662257728</v>
       </c>
       <c r="D54">
-        <v>18.12630904800938</v>
+        <v>17.84997337742272</v>
       </c>
       <c r="E54">
-        <v>28.504</v>
+        <v>29.28100000000001</v>
       </c>
       <c r="F54">
-        <v>40.404</v>
+        <v>41.181</v>
       </c>
       <c r="G54">
         <v>1.87</v>
@@ -5849,37 +5849,37 @@
         <v>2.16</v>
       </c>
       <c r="M54">
-        <v>9.527263200000002</v>
+        <v>9.710479800000002</v>
       </c>
       <c r="N54">
-        <v>-7.367263200000002</v>
+        <v>-7.550479800000002</v>
       </c>
       <c r="O54">
-        <v>-1.473452640000001</v>
+        <v>-1.51009596</v>
       </c>
       <c r="P54">
-        <v>-5.893810560000001</v>
+        <v>-6.040383840000001</v>
       </c>
       <c r="Q54">
-        <v>-4.693810560000001</v>
+        <v>-4.840383840000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1072392331629545</v>
+        <v>0.1085464508898259</v>
       </c>
       <c r="T54">
-        <v>1.197565011130533</v>
+        <v>1.223045117750332</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04534355679393847</v>
+        <v>0.04448801798650567</v>
       </c>
       <c r="W54">
-        <v>0.2251079893079893</v>
+        <v>0.225309725358782</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2267177839696923</v>
+        <v>0.2224400899325283</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1704309863583726</v>
+        <v>0.1723309863583726</v>
       </c>
       <c r="C55">
-        <v>-21.46102662257728</v>
+        <v>-22.50606333353001</v>
       </c>
       <c r="D55">
-        <v>17.84997337742272</v>
+        <v>17.58193666647</v>
       </c>
       <c r="E55">
-        <v>29.28100000000001</v>
+        <v>30.05800000000001</v>
       </c>
       <c r="F55">
-        <v>41.181</v>
+        <v>41.95800000000001</v>
       </c>
       <c r="G55">
         <v>1.87</v>
@@ -5931,37 +5931,37 @@
         <v>2.16</v>
       </c>
       <c r="M55">
-        <v>9.710479800000002</v>
+        <v>9.893696400000001</v>
       </c>
       <c r="N55">
-        <v>-7.550479800000002</v>
+        <v>-7.733696400000001</v>
       </c>
       <c r="O55">
-        <v>-1.51009596</v>
+        <v>-1.54673928</v>
       </c>
       <c r="P55">
-        <v>-6.040383840000001</v>
+        <v>-6.186957120000001</v>
       </c>
       <c r="Q55">
-        <v>-4.840383840000001</v>
+        <v>-4.986957120000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1085464508898259</v>
+        <v>0.1099105041700395</v>
       </c>
       <c r="T55">
-        <v>1.223045117750332</v>
+        <v>1.24963305509273</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04448801798650567</v>
+        <v>0.04366416580157038</v>
       </c>
       <c r="W55">
-        <v>0.225309725358782</v>
+        <v>0.2255039897039897</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2224400899325283</v>
+        <v>0.2183208290078519</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1723309863583726</v>
+        <v>0.1742309863583726</v>
       </c>
       <c r="C56">
-        <v>-22.50606333353001</v>
+        <v>-23.54316940772209</v>
       </c>
       <c r="D56">
-        <v>17.58193666647</v>
+        <v>17.32183059227791</v>
       </c>
       <c r="E56">
-        <v>30.05800000000001</v>
+        <v>30.83500000000001</v>
       </c>
       <c r="F56">
-        <v>41.95800000000001</v>
+        <v>42.73500000000001</v>
       </c>
       <c r="G56">
         <v>1.87</v>
@@ -6013,37 +6013,37 @@
         <v>2.16</v>
       </c>
       <c r="M56">
-        <v>9.893696400000001</v>
+        <v>10.076913</v>
       </c>
       <c r="N56">
-        <v>-7.733696400000001</v>
+        <v>-7.916913000000001</v>
       </c>
       <c r="O56">
-        <v>-1.54673928</v>
+        <v>-1.5833826</v>
       </c>
       <c r="P56">
-        <v>-6.186957120000001</v>
+        <v>-6.333530400000001</v>
       </c>
       <c r="Q56">
-        <v>-4.986957120000001</v>
+        <v>-5.133530400000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1099105041700395</v>
+        <v>0.1113351820404848</v>
       </c>
       <c r="T56">
-        <v>1.24963305509273</v>
+        <v>1.277402678539235</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04366416580157038</v>
+        <v>0.04287027187790547</v>
       </c>
       <c r="W56">
-        <v>0.2255039897039897</v>
+        <v>0.2256911898911899</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2183208290078519</v>
+        <v>0.2143513593895273</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1742309863583726</v>
+        <v>0.1761309863583727</v>
       </c>
       <c r="C57">
-        <v>-23.54316940772209</v>
+        <v>-24.57269168998912</v>
       </c>
       <c r="D57">
-        <v>17.32183059227791</v>
+        <v>17.06930831001089</v>
       </c>
       <c r="E57">
-        <v>30.83500000000001</v>
+        <v>31.61200000000001</v>
       </c>
       <c r="F57">
-        <v>42.73500000000001</v>
+        <v>43.51200000000001</v>
       </c>
       <c r="G57">
         <v>1.87</v>
@@ -6095,37 +6095,37 @@
         <v>2.16</v>
       </c>
       <c r="M57">
-        <v>10.076913</v>
+        <v>10.2601296</v>
       </c>
       <c r="N57">
-        <v>-7.916913000000001</v>
+        <v>-8.100129600000002</v>
       </c>
       <c r="O57">
-        <v>-1.5833826</v>
+        <v>-1.620025920000001</v>
       </c>
       <c r="P57">
-        <v>-6.333530400000001</v>
+        <v>-6.480103680000002</v>
       </c>
       <c r="Q57">
-        <v>-5.133530400000001</v>
+        <v>-5.280103680000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1113351820404848</v>
+        <v>0.1128246179959504</v>
       </c>
       <c r="T57">
-        <v>1.277402678539235</v>
+        <v>1.306434557596945</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04287027187790547</v>
+        <v>0.04210473130865715</v>
       </c>
       <c r="W57">
-        <v>0.2256911898911899</v>
+        <v>0.2258717043574187</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2143513593895273</v>
+        <v>0.2105236565432858</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1761309863583727</v>
+        <v>0.1780309863583726</v>
       </c>
       <c r="C58">
-        <v>-24.57269168998912</v>
+        <v>-25.59495709019663</v>
       </c>
       <c r="D58">
-        <v>17.06930831001089</v>
+        <v>16.82404290980337</v>
       </c>
       <c r="E58">
-        <v>31.61200000000001</v>
+        <v>32.38900000000001</v>
       </c>
       <c r="F58">
-        <v>43.51200000000001</v>
+        <v>44.28900000000001</v>
       </c>
       <c r="G58">
         <v>1.87</v>
@@ -6177,37 +6177,37 @@
         <v>2.16</v>
       </c>
       <c r="M58">
-        <v>10.2601296</v>
+        <v>10.4433462</v>
       </c>
       <c r="N58">
-        <v>-8.100129600000002</v>
+        <v>-8.283346200000002</v>
       </c>
       <c r="O58">
-        <v>-1.620025920000001</v>
+        <v>-1.65666924</v>
       </c>
       <c r="P58">
-        <v>-6.480103680000002</v>
+        <v>-6.626676960000002</v>
       </c>
       <c r="Q58">
-        <v>-5.280103680000002</v>
+        <v>-5.426676960000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1128246179959504</v>
+        <v>0.1143833300423679</v>
       </c>
       <c r="T58">
-        <v>1.306434557596945</v>
+        <v>1.336816756610828</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04210473130865715</v>
+        <v>0.04136605181201404</v>
       </c>
       <c r="W58">
-        <v>0.2258717043574187</v>
+        <v>0.2260458849827271</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2105236565432858</v>
+        <v>0.2068302590600702</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1780309863583726</v>
+        <v>0.1799309863583726</v>
       </c>
       <c r="C59">
-        <v>-25.59495709019663</v>
+        <v>-26.61027399516012</v>
       </c>
       <c r="D59">
-        <v>16.82404290980337</v>
+        <v>16.58572600483989</v>
       </c>
       <c r="E59">
-        <v>32.38900000000001</v>
+        <v>33.16600000000001</v>
       </c>
       <c r="F59">
-        <v>44.28900000000001</v>
+        <v>45.06600000000001</v>
       </c>
       <c r="G59">
         <v>1.87</v>
@@ -6259,37 +6259,37 @@
         <v>2.16</v>
       </c>
       <c r="M59">
-        <v>10.4433462</v>
+        <v>10.6265628</v>
       </c>
       <c r="N59">
-        <v>-8.283346200000002</v>
+        <v>-8.466562800000002</v>
       </c>
       <c r="O59">
-        <v>-1.65666924</v>
+        <v>-1.693312560000001</v>
       </c>
       <c r="P59">
-        <v>-6.626676960000002</v>
+        <v>-6.773250240000001</v>
       </c>
       <c r="Q59">
-        <v>-5.426676960000002</v>
+        <v>-5.573250240000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1143833300423679</v>
+        <v>0.116016266471948</v>
       </c>
       <c r="T59">
-        <v>1.336816756610828</v>
+        <v>1.368645727006324</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04136605181201404</v>
+        <v>0.04065284402215173</v>
       </c>
       <c r="W59">
-        <v>0.2260458849827271</v>
+        <v>0.2262140593795766</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2068302590600702</v>
+        <v>0.2032642201107586</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1799309863583726</v>
+        <v>0.1818309863583726</v>
       </c>
       <c r="C60">
-        <v>-26.61027399516009</v>
+        <v>-27.61893356223973</v>
       </c>
       <c r="D60">
-        <v>16.5857260048399</v>
+        <v>16.35406643776027</v>
       </c>
       <c r="E60">
-        <v>33.166</v>
+        <v>33.943</v>
       </c>
       <c r="F60">
-        <v>45.066</v>
+        <v>45.843</v>
       </c>
       <c r="G60">
         <v>1.87</v>
@@ -6341,37 +6341,37 @@
         <v>2.16</v>
       </c>
       <c r="M60">
-        <v>10.6265628</v>
+        <v>10.8097794</v>
       </c>
       <c r="N60">
-        <v>-8.466562799999998</v>
+        <v>-8.6497794</v>
       </c>
       <c r="O60">
-        <v>-1.69331256</v>
+        <v>-1.72995588</v>
       </c>
       <c r="P60">
-        <v>-6.773250239999999</v>
+        <v>-6.91982352</v>
       </c>
       <c r="Q60">
-        <v>-5.573250239999998</v>
+        <v>-5.71982352</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.116016266471948</v>
+        <v>0.1177288583371175</v>
       </c>
       <c r="T60">
-        <v>1.368645727006323</v>
+        <v>1.402027330104038</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04065284402215175</v>
+        <v>0.039963812767539</v>
       </c>
       <c r="W60">
-        <v>0.2262140593795766</v>
+        <v>0.2263765329494143</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2032642201107587</v>
+        <v>0.199819063837695</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1818309863583726</v>
+        <v>0.1837309863583726</v>
       </c>
       <c r="C61">
-        <v>-27.61893356223973</v>
+        <v>-28.62121090601955</v>
       </c>
       <c r="D61">
-        <v>16.35406643776027</v>
+        <v>16.12878909398045</v>
       </c>
       <c r="E61">
-        <v>33.943</v>
+        <v>34.72</v>
       </c>
       <c r="F61">
-        <v>45.843</v>
+        <v>46.62</v>
       </c>
       <c r="G61">
         <v>1.87</v>
@@ -6423,37 +6423,37 @@
         <v>2.16</v>
       </c>
       <c r="M61">
-        <v>10.8097794</v>
+        <v>10.992996</v>
       </c>
       <c r="N61">
-        <v>-8.6497794</v>
+        <v>-8.832996</v>
       </c>
       <c r="O61">
-        <v>-1.72995588</v>
+        <v>-1.7665992</v>
       </c>
       <c r="P61">
-        <v>-6.91982352</v>
+        <v>-7.0663968</v>
       </c>
       <c r="Q61">
-        <v>-5.71982352</v>
+        <v>-5.8663968</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1177288583371175</v>
+        <v>0.1195270797955454</v>
       </c>
       <c r="T61">
-        <v>1.402027330104038</v>
+        <v>1.437078013356639</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.039963812767539</v>
+        <v>0.03929774922141335</v>
       </c>
       <c r="W61">
-        <v>0.2263765329494143</v>
+        <v>0.2265335907335907</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.199819063837695</v>
+        <v>0.1964887461070667</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1837309863583726</v>
+        <v>0.1856309863583726</v>
       </c>
       <c r="C62">
-        <v>-28.62121090601955</v>
+        <v>-29.61736618824021</v>
       </c>
       <c r="D62">
-        <v>16.12878909398045</v>
+        <v>15.90963381175979</v>
       </c>
       <c r="E62">
-        <v>34.72</v>
+        <v>35.497</v>
       </c>
       <c r="F62">
-        <v>46.62</v>
+        <v>47.397</v>
       </c>
       <c r="G62">
         <v>1.87</v>
@@ -6505,37 +6505,37 @@
         <v>2.16</v>
       </c>
       <c r="M62">
-        <v>10.992996</v>
+        <v>11.1762126</v>
       </c>
       <c r="N62">
-        <v>-8.832996</v>
+        <v>-9.016212599999999</v>
       </c>
       <c r="O62">
-        <v>-1.7665992</v>
+        <v>-1.80324252</v>
       </c>
       <c r="P62">
-        <v>-7.0663968</v>
+        <v>-7.21297008</v>
       </c>
       <c r="Q62">
-        <v>-5.8663968</v>
+        <v>-6.012970080000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1195270797955454</v>
+        <v>0.121417517739021</v>
       </c>
       <c r="T62">
-        <v>1.437078013356639</v>
+        <v>1.473926167545271</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03929774922141335</v>
+        <v>0.038653523824341</v>
       </c>
       <c r="W62">
-        <v>0.2265335907335907</v>
+        <v>0.2266854990822204</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1964887461070667</v>
+        <v>0.193267619121705</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1856309863583726</v>
+        <v>0.1875309863583726</v>
       </c>
       <c r="C63">
-        <v>-29.61736618824021</v>
+        <v>-30.60764562006403</v>
       </c>
       <c r="D63">
-        <v>15.90963381175979</v>
+        <v>15.69635437993597</v>
       </c>
       <c r="E63">
-        <v>35.497</v>
+        <v>36.274</v>
       </c>
       <c r="F63">
-        <v>47.397</v>
+        <v>48.174</v>
       </c>
       <c r="G63">
         <v>1.87</v>
@@ -6587,37 +6587,37 @@
         <v>2.16</v>
       </c>
       <c r="M63">
-        <v>11.1762126</v>
+        <v>11.3594292</v>
       </c>
       <c r="N63">
-        <v>-9.016212599999999</v>
+        <v>-9.199429200000001</v>
       </c>
       <c r="O63">
-        <v>-1.80324252</v>
+        <v>-1.83988584</v>
       </c>
       <c r="P63">
-        <v>-7.21297008</v>
+        <v>-7.359543360000001</v>
       </c>
       <c r="Q63">
-        <v>-6.012970080000001</v>
+        <v>-6.159543360000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.121417517739021</v>
+        <v>0.1234074524163636</v>
       </c>
       <c r="T63">
-        <v>1.473926167545271</v>
+        <v>1.512713698270147</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.038653523824341</v>
+        <v>0.03803007989169033</v>
       </c>
       <c r="W63">
-        <v>0.2266854990822204</v>
+        <v>0.2268325071615394</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.193267619121705</v>
+        <v>0.1901503994584517</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1875309863583726</v>
+        <v>0.1894309863583726</v>
       </c>
       <c r="C64">
-        <v>-30.60764562006403</v>
+        <v>-31.59228238479019</v>
       </c>
       <c r="D64">
-        <v>15.69635437993597</v>
+        <v>15.48871761520981</v>
       </c>
       <c r="E64">
-        <v>36.274</v>
+        <v>37.051</v>
       </c>
       <c r="F64">
-        <v>48.174</v>
+        <v>48.951</v>
       </c>
       <c r="G64">
         <v>1.87</v>
@@ -6669,37 +6669,37 @@
         <v>2.16</v>
       </c>
       <c r="M64">
-        <v>11.3594292</v>
+        <v>11.5426458</v>
       </c>
       <c r="N64">
-        <v>-9.199429200000001</v>
+        <v>-9.382645800000001</v>
       </c>
       <c r="O64">
-        <v>-1.83988584</v>
+        <v>-1.87652916</v>
       </c>
       <c r="P64">
-        <v>-7.359543360000001</v>
+        <v>-7.50611664</v>
       </c>
       <c r="Q64">
-        <v>-6.159543360000001</v>
+        <v>-6.306116640000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1234074524163636</v>
+        <v>0.1255049511303194</v>
       </c>
       <c r="T64">
-        <v>1.512713698270147</v>
+        <v>1.553597852277448</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03803007989169033</v>
+        <v>0.03742642782991747</v>
       </c>
       <c r="W64">
-        <v>0.2268325071615394</v>
+        <v>0.2269748483177055</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1901503994584517</v>
+        <v>0.1871321391495874</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1894309863583726</v>
+        <v>0.1913309863583726</v>
       </c>
       <c r="C65">
-        <v>-31.59228238479019</v>
+        <v>-32.57149748829008</v>
       </c>
       <c r="D65">
-        <v>15.48871761520981</v>
+        <v>15.28650251170993</v>
       </c>
       <c r="E65">
-        <v>37.051</v>
+        <v>37.828</v>
       </c>
       <c r="F65">
-        <v>48.951</v>
+        <v>49.728</v>
       </c>
       <c r="G65">
         <v>1.87</v>
@@ -6751,37 +6751,37 @@
         <v>2.16</v>
       </c>
       <c r="M65">
-        <v>11.5426458</v>
+        <v>11.7258624</v>
       </c>
       <c r="N65">
-        <v>-9.382645800000001</v>
+        <v>-9.5658624</v>
       </c>
       <c r="O65">
-        <v>-1.87652916</v>
+        <v>-1.91317248</v>
       </c>
       <c r="P65">
-        <v>-7.50611664</v>
+        <v>-7.65268992</v>
       </c>
       <c r="Q65">
-        <v>-6.306116640000001</v>
+        <v>-6.452689920000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1255049511303194</v>
+        <v>0.127718977550606</v>
       </c>
       <c r="T65">
-        <v>1.553597852277448</v>
+        <v>1.596753348174044</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03742642782991747</v>
+        <v>0.03684163989507502</v>
       </c>
       <c r="W65">
-        <v>0.2269748483177055</v>
+        <v>0.2271127413127413</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1871321391495874</v>
+        <v>0.184208199475375</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1913309863583726</v>
+        <v>0.1932309863583726</v>
       </c>
       <c r="C66">
-        <v>-32.57149748829008</v>
+        <v>-33.54550054368338</v>
       </c>
       <c r="D66">
-        <v>15.28650251170993</v>
+        <v>15.08949945631662</v>
       </c>
       <c r="E66">
-        <v>37.828</v>
+        <v>38.605</v>
       </c>
       <c r="F66">
-        <v>49.728</v>
+        <v>50.505</v>
       </c>
       <c r="G66">
         <v>1.87</v>
@@ -6833,37 +6833,37 @@
         <v>2.16</v>
       </c>
       <c r="M66">
-        <v>11.7258624</v>
+        <v>11.909079</v>
       </c>
       <c r="N66">
-        <v>-9.5658624</v>
+        <v>-9.749079000000002</v>
       </c>
       <c r="O66">
-        <v>-1.91317248</v>
+        <v>-1.949815800000001</v>
       </c>
       <c r="P66">
-        <v>-7.65268992</v>
+        <v>-7.799263200000001</v>
       </c>
       <c r="Q66">
-        <v>-6.452689920000001</v>
+        <v>-6.599263200000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.127718977550606</v>
+        <v>0.1300595197663376</v>
       </c>
       <c r="T66">
-        <v>1.596753348174044</v>
+        <v>1.642374872407588</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03684163989507502</v>
+        <v>0.03627484543515078</v>
       </c>
       <c r="W66">
-        <v>0.2271127413127413</v>
+        <v>0.2272463914463914</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.184208199475375</v>
+        <v>0.1813742271757539</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1932309863583726</v>
+        <v>0.1951309863583726</v>
       </c>
       <c r="C67">
-        <v>-33.54550054368338</v>
+        <v>-34.51449049611159</v>
       </c>
       <c r="D67">
-        <v>15.08949945631662</v>
+        <v>14.89750950388841</v>
       </c>
       <c r="E67">
-        <v>38.605</v>
+        <v>39.38200000000001</v>
       </c>
       <c r="F67">
-        <v>50.505</v>
+        <v>51.282</v>
       </c>
       <c r="G67">
         <v>1.87</v>
@@ -6915,37 +6915,37 @@
         <v>2.16</v>
       </c>
       <c r="M67">
-        <v>11.909079</v>
+        <v>12.0922956</v>
       </c>
       <c r="N67">
-        <v>-9.749079000000002</v>
+        <v>-9.932295600000002</v>
       </c>
       <c r="O67">
-        <v>-1.949815800000001</v>
+        <v>-1.98645912</v>
       </c>
       <c r="P67">
-        <v>-7.799263200000001</v>
+        <v>-7.945836480000001</v>
       </c>
       <c r="Q67">
-        <v>-6.599263200000001</v>
+        <v>-6.745836480000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1300595197663376</v>
+        <v>0.1325377409359358</v>
       </c>
       <c r="T67">
-        <v>1.642374872407588</v>
+        <v>1.690680015713694</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03627484543515078</v>
+        <v>0.03572522656492122</v>
       </c>
       <c r="W67">
-        <v>0.2272463914463914</v>
+        <v>0.2273759915759916</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1813742271757539</v>
+        <v>0.178626132824606</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1951309863583726</v>
+        <v>0.1970309863583726</v>
       </c>
       <c r="C68">
-        <v>-34.51449049611159</v>
+        <v>-35.47865629287703</v>
       </c>
       <c r="D68">
-        <v>14.89750950388841</v>
+        <v>14.71034370712297</v>
       </c>
       <c r="E68">
-        <v>39.38200000000001</v>
+        <v>40.15900000000001</v>
       </c>
       <c r="F68">
-        <v>51.282</v>
+        <v>52.059</v>
       </c>
       <c r="G68">
         <v>1.87</v>
@@ -6997,37 +6997,37 @@
         <v>2.16</v>
       </c>
       <c r="M68">
-        <v>12.0922956</v>
+        <v>12.2755122</v>
       </c>
       <c r="N68">
-        <v>-9.932295600000002</v>
+        <v>-10.1155122</v>
       </c>
       <c r="O68">
-        <v>-1.98645912</v>
+        <v>-2.02310244</v>
       </c>
       <c r="P68">
-        <v>-7.945836480000001</v>
+        <v>-8.092409760000001</v>
       </c>
       <c r="Q68">
-        <v>-6.745836480000001</v>
+        <v>-6.892409760000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1325377409359358</v>
+        <v>0.1351661573279339</v>
       </c>
       <c r="T68">
-        <v>1.690680015713694</v>
+        <v>1.741912743462594</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03572522656492122</v>
+        <v>0.03519201422813135</v>
       </c>
       <c r="W68">
-        <v>0.2273759915759916</v>
+        <v>0.2275017230450066</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.178626132824606</v>
+        <v>0.1759600711406567</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1970309863583726</v>
+        <v>0.1989309863583726</v>
       </c>
       <c r="C69">
-        <v>-35.47865629287703</v>
+        <v>-36.43817750369274</v>
       </c>
       <c r="D69">
-        <v>14.71034370712297</v>
+        <v>14.52782249630726</v>
       </c>
       <c r="E69">
-        <v>40.15900000000001</v>
+        <v>40.93600000000001</v>
       </c>
       <c r="F69">
-        <v>52.059</v>
+        <v>52.83600000000001</v>
       </c>
       <c r="G69">
         <v>1.87</v>
@@ -7079,37 +7079,37 @@
         <v>2.16</v>
       </c>
       <c r="M69">
-        <v>12.2755122</v>
+        <v>12.4587288</v>
       </c>
       <c r="N69">
-        <v>-10.1155122</v>
+        <v>-10.2987288</v>
       </c>
       <c r="O69">
-        <v>-2.02310244</v>
+        <v>-2.05974576</v>
       </c>
       <c r="P69">
-        <v>-8.092409760000001</v>
+        <v>-8.238983040000001</v>
       </c>
       <c r="Q69">
-        <v>-6.892409760000001</v>
+        <v>-7.038983040000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1351661573279339</v>
+        <v>0.1379588497444318</v>
       </c>
       <c r="T69">
-        <v>1.741912743462594</v>
+        <v>1.7963475166958</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03519201422813135</v>
+        <v>0.03467448460712942</v>
       </c>
       <c r="W69">
-        <v>0.2275017230450066</v>
+        <v>0.2276237565296389</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1759600711406567</v>
+        <v>0.1733724230356471</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1989309863583726</v>
+        <v>0.2008309863583726</v>
       </c>
       <c r="C70">
-        <v>-36.43817750369274</v>
+        <v>-37.39322489532306</v>
       </c>
       <c r="D70">
-        <v>14.52782249630726</v>
+        <v>14.34977510467695</v>
       </c>
       <c r="E70">
-        <v>40.93600000000001</v>
+        <v>41.71300000000001</v>
       </c>
       <c r="F70">
-        <v>52.83600000000001</v>
+        <v>53.61300000000001</v>
       </c>
       <c r="G70">
         <v>1.87</v>
@@ -7161,37 +7161,37 @@
         <v>2.16</v>
       </c>
       <c r="M70">
-        <v>12.4587288</v>
+        <v>12.6419454</v>
       </c>
       <c r="N70">
-        <v>-10.2987288</v>
+        <v>-10.4819454</v>
       </c>
       <c r="O70">
-        <v>-2.05974576</v>
+        <v>-2.096389080000001</v>
       </c>
       <c r="P70">
-        <v>-8.238983040000001</v>
+        <v>-8.385556320000003</v>
       </c>
       <c r="Q70">
-        <v>-7.038983040000002</v>
+        <v>-7.185556320000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1379588497444318</v>
+        <v>0.1409317158652199</v>
       </c>
       <c r="T70">
-        <v>1.7963475166958</v>
+        <v>1.854294210782761</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03467448460712942</v>
+        <v>0.03417195584470725</v>
       </c>
       <c r="W70">
-        <v>0.2276237565296389</v>
+        <v>0.227742252811818</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1733724230356471</v>
+        <v>0.1708597792235362</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2008309863583726</v>
+        <v>0.2027309863583726</v>
       </c>
       <c r="C71">
-        <v>-37.39322489532306</v>
+        <v>-38.3439609644804</v>
       </c>
       <c r="D71">
-        <v>14.34977510467695</v>
+        <v>14.17603903551961</v>
       </c>
       <c r="E71">
-        <v>41.71300000000001</v>
+        <v>42.49000000000001</v>
       </c>
       <c r="F71">
-        <v>53.61300000000001</v>
+        <v>54.39000000000001</v>
       </c>
       <c r="G71">
         <v>1.87</v>
@@ -7243,37 +7243,37 @@
         <v>2.16</v>
       </c>
       <c r="M71">
-        <v>12.6419454</v>
+        <v>12.825162</v>
       </c>
       <c r="N71">
-        <v>-10.4819454</v>
+        <v>-10.665162</v>
       </c>
       <c r="O71">
-        <v>-2.096389080000001</v>
+        <v>-2.133032400000001</v>
       </c>
       <c r="P71">
-        <v>-8.385556320000003</v>
+        <v>-8.532129600000001</v>
       </c>
       <c r="Q71">
-        <v>-7.185556320000003</v>
+        <v>-7.332129600000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1409317158652199</v>
+        <v>0.1441027730607273</v>
       </c>
       <c r="T71">
-        <v>1.854294210782761</v>
+        <v>1.916104017808853</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03417195584470725</v>
+        <v>0.03368378504692572</v>
       </c>
       <c r="W71">
-        <v>0.227742252811818</v>
+        <v>0.2278573634859349</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1708597792235362</v>
+        <v>0.1684189252346286</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2027309863583726</v>
+        <v>0.2046309863583727</v>
       </c>
       <c r="C72">
-        <v>-38.3439609644804</v>
+        <v>-39.29054043247359</v>
       </c>
       <c r="D72">
-        <v>14.17603903551961</v>
+        <v>14.00645956752642</v>
       </c>
       <c r="E72">
-        <v>42.49000000000001</v>
+        <v>43.26700000000001</v>
       </c>
       <c r="F72">
-        <v>54.39000000000001</v>
+        <v>55.16700000000001</v>
       </c>
       <c r="G72">
         <v>1.87</v>
@@ -7325,37 +7325,37 @@
         <v>2.16</v>
       </c>
       <c r="M72">
-        <v>12.825162</v>
+        <v>13.0083786</v>
       </c>
       <c r="N72">
-        <v>-10.665162</v>
+        <v>-10.8483786</v>
       </c>
       <c r="O72">
-        <v>-2.133032400000001</v>
+        <v>-2.16967572</v>
       </c>
       <c r="P72">
-        <v>-8.532129600000001</v>
+        <v>-8.678702880000001</v>
       </c>
       <c r="Q72">
-        <v>-7.332129600000002</v>
+        <v>-7.478702880000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1441027730607273</v>
+        <v>0.1474925238559248</v>
       </c>
       <c r="T72">
-        <v>1.916104017808853</v>
+        <v>1.98217657014709</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03368378504692572</v>
+        <v>0.03320936553922254</v>
       </c>
       <c r="W72">
-        <v>0.2278573634859349</v>
+        <v>0.2279692316058513</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1684189252346286</v>
+        <v>0.1660468276961127</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2046309863583726</v>
+        <v>0.2065309863583726</v>
       </c>
       <c r="C73">
-        <v>-39.29054043247358</v>
+        <v>-40.23311070477294</v>
       </c>
       <c r="D73">
-        <v>14.00645956752642</v>
+        <v>13.84088929522706</v>
       </c>
       <c r="E73">
-        <v>43.267</v>
+        <v>44.044</v>
       </c>
       <c r="F73">
-        <v>55.167</v>
+        <v>55.944</v>
       </c>
       <c r="G73">
         <v>1.87</v>
@@ -7407,37 +7407,37 @@
         <v>2.16</v>
       </c>
       <c r="M73">
-        <v>13.0083786</v>
+        <v>13.1915952</v>
       </c>
       <c r="N73">
-        <v>-10.8483786</v>
+        <v>-11.0315952</v>
       </c>
       <c r="O73">
-        <v>-2.16967572</v>
+        <v>-2.20631904</v>
       </c>
       <c r="P73">
-        <v>-8.678702879999999</v>
+        <v>-8.825276160000001</v>
       </c>
       <c r="Q73">
-        <v>-7.47870288</v>
+        <v>-7.625276160000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1474925238559247</v>
+        <v>0.151124399707922</v>
       </c>
       <c r="T73">
-        <v>1.982176570147089</v>
+        <v>2.052968590509485</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03320936553922255</v>
+        <v>0.03274812435117778</v>
       </c>
       <c r="W73">
-        <v>0.2279692316058513</v>
+        <v>0.2280779922779923</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1660468276961127</v>
+        <v>0.1637406217558889</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2065309863583726</v>
+        <v>0.2084309863583726</v>
       </c>
       <c r="C74">
-        <v>-40.23311070477294</v>
+        <v>-41.1718122983609</v>
       </c>
       <c r="D74">
-        <v>13.84088929522706</v>
+        <v>13.67918770163909</v>
       </c>
       <c r="E74">
-        <v>44.044</v>
+        <v>44.82100000000001</v>
       </c>
       <c r="F74">
-        <v>55.944</v>
+        <v>56.721</v>
       </c>
       <c r="G74">
         <v>1.87</v>
@@ -7489,37 +7489,37 @@
         <v>2.16</v>
       </c>
       <c r="M74">
-        <v>13.1915952</v>
+        <v>13.3748118</v>
       </c>
       <c r="N74">
-        <v>-11.0315952</v>
+        <v>-11.2148118</v>
       </c>
       <c r="O74">
-        <v>-2.20631904</v>
+        <v>-2.24296236</v>
       </c>
       <c r="P74">
-        <v>-8.825276160000001</v>
+        <v>-8.971849440000002</v>
       </c>
       <c r="Q74">
-        <v>-7.625276160000002</v>
+        <v>-7.771849440000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.151124399707922</v>
+        <v>0.155025303400808</v>
       </c>
       <c r="T74">
-        <v>2.052968590509485</v>
+        <v>2.129004464232058</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03274812435117778</v>
+        <v>0.03229951990801096</v>
       </c>
       <c r="W74">
-        <v>0.2280779922779923</v>
+        <v>0.228183773205691</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1637406217558889</v>
+        <v>0.1614975995400548</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2084309863583726</v>
+        <v>0.2103309863583726</v>
       </c>
       <c r="C75">
-        <v>-41.1718122983609</v>
+        <v>-42.10677923947256</v>
       </c>
       <c r="D75">
-        <v>13.67918770163909</v>
+        <v>13.52122076052745</v>
       </c>
       <c r="E75">
-        <v>44.82100000000001</v>
+        <v>45.59800000000001</v>
       </c>
       <c r="F75">
-        <v>56.721</v>
+        <v>57.498</v>
       </c>
       <c r="G75">
         <v>1.87</v>
@@ -7571,37 +7571,37 @@
         <v>2.16</v>
       </c>
       <c r="M75">
-        <v>13.3748118</v>
+        <v>13.5580284</v>
       </c>
       <c r="N75">
-        <v>-11.2148118</v>
+        <v>-11.3980284</v>
       </c>
       <c r="O75">
-        <v>-2.24296236</v>
+        <v>-2.27960568</v>
       </c>
       <c r="P75">
-        <v>-8.971849440000002</v>
+        <v>-9.118422720000002</v>
       </c>
       <c r="Q75">
-        <v>-7.771849440000002</v>
+        <v>-7.918422720000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.155025303400808</v>
+        <v>0.1592262766085314</v>
       </c>
       <c r="T75">
-        <v>2.129004464232058</v>
+        <v>2.210889251317907</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03229951990801096</v>
+        <v>0.03186303990925406</v>
       </c>
       <c r="W75">
-        <v>0.228183773205691</v>
+        <v>0.2282866951893979</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1614975995400548</v>
+        <v>0.1593151995462703</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2103309863583726</v>
+        <v>0.2122309863583726</v>
       </c>
       <c r="C76">
-        <v>-42.10677923947256</v>
+        <v>-43.03813943409211</v>
       </c>
       <c r="D76">
-        <v>13.52122076052745</v>
+        <v>13.3668605659079</v>
       </c>
       <c r="E76">
-        <v>45.59800000000001</v>
+        <v>46.37500000000001</v>
       </c>
       <c r="F76">
-        <v>57.498</v>
+        <v>58.27500000000001</v>
       </c>
       <c r="G76">
         <v>1.87</v>
@@ -7653,37 +7653,37 @@
         <v>2.16</v>
       </c>
       <c r="M76">
-        <v>13.5580284</v>
+        <v>13.741245</v>
       </c>
       <c r="N76">
-        <v>-11.3980284</v>
+        <v>-11.581245</v>
       </c>
       <c r="O76">
-        <v>-2.27960568</v>
+        <v>-2.316249</v>
       </c>
       <c r="P76">
-        <v>-9.118422720000002</v>
+        <v>-9.264996</v>
       </c>
       <c r="Q76">
-        <v>-7.918422720000002</v>
+        <v>-8.064996000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1592262766085314</v>
+        <v>0.1637633276728727</v>
       </c>
       <c r="T76">
-        <v>2.210889251317907</v>
+        <v>2.299324821370623</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03186303990925406</v>
+        <v>0.03143819937713068</v>
       </c>
       <c r="W76">
-        <v>0.2282866951893979</v>
+        <v>0.2283868725868726</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1593151995462703</v>
+        <v>0.1571909968856534</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2122309863583726</v>
+        <v>0.2141309863583726</v>
       </c>
       <c r="C77">
-        <v>-43.03813943409211</v>
+        <v>-43.96601501335803</v>
       </c>
       <c r="D77">
-        <v>13.3668605659079</v>
+        <v>13.21598498664196</v>
       </c>
       <c r="E77">
-        <v>46.37500000000001</v>
+        <v>47.152</v>
       </c>
       <c r="F77">
-        <v>58.27500000000001</v>
+        <v>59.052</v>
       </c>
       <c r="G77">
         <v>1.87</v>
@@ -7735,37 +7735,37 @@
         <v>2.16</v>
       </c>
       <c r="M77">
-        <v>13.741245</v>
+        <v>13.9244616</v>
       </c>
       <c r="N77">
-        <v>-11.581245</v>
+        <v>-11.7644616</v>
       </c>
       <c r="O77">
-        <v>-2.316249</v>
+        <v>-2.35289232</v>
       </c>
       <c r="P77">
-        <v>-9.264996</v>
+        <v>-9.41156928</v>
       </c>
       <c r="Q77">
-        <v>-8.064996000000001</v>
+        <v>-8.211569280000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1637633276728727</v>
+        <v>0.1686784663259091</v>
       </c>
       <c r="T77">
-        <v>2.299324821370623</v>
+        <v>2.395130022261066</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03143819937713068</v>
+        <v>0.03102453885901054</v>
       </c>
       <c r="W77">
-        <v>0.2283868725868726</v>
+        <v>0.2284844137370453</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1571909968856534</v>
+        <v>0.1551226942950527</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2141309863583726</v>
+        <v>0.2160309863583726</v>
       </c>
       <c r="C78">
-        <v>-43.96601501335803</v>
+        <v>-44.89052265583716</v>
       </c>
       <c r="D78">
-        <v>13.21598498664196</v>
+        <v>13.06847734416284</v>
       </c>
       <c r="E78">
-        <v>47.152</v>
+        <v>47.929</v>
       </c>
       <c r="F78">
-        <v>59.052</v>
+        <v>59.829</v>
       </c>
       <c r="G78">
         <v>1.87</v>
@@ -7817,37 +7817,37 @@
         <v>2.16</v>
       </c>
       <c r="M78">
-        <v>13.9244616</v>
+        <v>14.1076782</v>
       </c>
       <c r="N78">
-        <v>-11.7644616</v>
+        <v>-11.9476782</v>
       </c>
       <c r="O78">
-        <v>-2.35289232</v>
+        <v>-2.38953564</v>
       </c>
       <c r="P78">
-        <v>-9.41156928</v>
+        <v>-9.55814256</v>
       </c>
       <c r="Q78">
-        <v>-8.211569280000001</v>
+        <v>-8.358142560000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1686784663259091</v>
+        <v>0.174021008340079</v>
       </c>
       <c r="T78">
-        <v>2.395130022261066</v>
+        <v>2.49926611018546</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03102453885901054</v>
+        <v>0.03062162276993248</v>
       </c>
       <c r="W78">
-        <v>0.2284844137370453</v>
+        <v>0.2285794213508499</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1551226942950527</v>
+        <v>0.1531081138496624</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2160309863583726</v>
+        <v>0.2179309863583727</v>
       </c>
       <c r="C79">
-        <v>-44.89052265583716</v>
+        <v>-45.81177388845494</v>
       </c>
       <c r="D79">
-        <v>13.06847734416284</v>
+        <v>12.92422611154506</v>
       </c>
       <c r="E79">
-        <v>47.929</v>
+        <v>48.706</v>
       </c>
       <c r="F79">
-        <v>59.829</v>
+        <v>60.606</v>
       </c>
       <c r="G79">
         <v>1.87</v>
@@ -7899,37 +7899,37 @@
         <v>2.16</v>
       </c>
       <c r="M79">
-        <v>14.1076782</v>
+        <v>14.2908948</v>
       </c>
       <c r="N79">
-        <v>-11.9476782</v>
+        <v>-12.1308948</v>
       </c>
       <c r="O79">
-        <v>-2.38953564</v>
+        <v>-2.42617896</v>
       </c>
       <c r="P79">
-        <v>-9.55814256</v>
+        <v>-9.70471584</v>
       </c>
       <c r="Q79">
-        <v>-8.358142560000001</v>
+        <v>-8.504715840000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.174021008340079</v>
+        <v>0.1798492359919008</v>
       </c>
       <c r="T79">
-        <v>2.49926611018546</v>
+        <v>2.612869115193891</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03062162276993248</v>
+        <v>0.03022903786262565</v>
       </c>
       <c r="W79">
-        <v>0.2285794213508499</v>
+        <v>0.2286719928719929</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1531081138496624</v>
+        <v>0.1511451893131283</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2179309863583727</v>
+        <v>0.2198309863583726</v>
       </c>
       <c r="C80">
-        <v>-45.81177388845494</v>
+        <v>-46.72987536771318</v>
       </c>
       <c r="D80">
-        <v>12.92422611154506</v>
+        <v>12.78312463228683</v>
       </c>
       <c r="E80">
-        <v>48.706</v>
+        <v>49.483</v>
       </c>
       <c r="F80">
-        <v>60.606</v>
+        <v>61.383</v>
       </c>
       <c r="G80">
         <v>1.87</v>
@@ -7981,37 +7981,37 @@
         <v>2.16</v>
       </c>
       <c r="M80">
-        <v>14.2908948</v>
+        <v>14.4741114</v>
       </c>
       <c r="N80">
-        <v>-12.1308948</v>
+        <v>-12.3141114</v>
       </c>
       <c r="O80">
-        <v>-2.42617896</v>
+        <v>-2.462822280000001</v>
       </c>
       <c r="P80">
-        <v>-9.70471584</v>
+        <v>-9.851289120000001</v>
       </c>
       <c r="Q80">
-        <v>-8.504715840000001</v>
+        <v>-8.651289120000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1798492359919008</v>
+        <v>0.1862325329438961</v>
       </c>
       <c r="T80">
-        <v>2.612869115193891</v>
+        <v>2.737291454012648</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03022903786262565</v>
+        <v>0.02984639181373165</v>
       </c>
       <c r="W80">
-        <v>0.2286719928719929</v>
+        <v>0.2287622208103221</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1511451893131283</v>
+        <v>0.1492319590686583</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2198309863583726</v>
+        <v>0.2217309863583726</v>
       </c>
       <c r="C81">
-        <v>-46.72987536771318</v>
+        <v>-47.64492914268531</v>
       </c>
       <c r="D81">
-        <v>12.78312463228683</v>
+        <v>12.64507085731469</v>
       </c>
       <c r="E81">
-        <v>49.483</v>
+        <v>50.26000000000001</v>
       </c>
       <c r="F81">
-        <v>61.383</v>
+        <v>62.16</v>
       </c>
       <c r="G81">
         <v>1.87</v>
@@ -8063,37 +8063,37 @@
         <v>2.16</v>
       </c>
       <c r="M81">
-        <v>14.4741114</v>
+        <v>14.657328</v>
       </c>
       <c r="N81">
-        <v>-12.3141114</v>
+        <v>-12.497328</v>
       </c>
       <c r="O81">
-        <v>-2.462822280000001</v>
+        <v>-2.499465600000001</v>
       </c>
       <c r="P81">
-        <v>-9.851289120000001</v>
+        <v>-9.997862400000001</v>
       </c>
       <c r="Q81">
-        <v>-8.651289120000001</v>
+        <v>-8.797862400000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1862325329438961</v>
+        <v>0.1932541595910909</v>
       </c>
       <c r="T81">
-        <v>2.737291454012648</v>
+        <v>2.87415602671328</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02984639181373165</v>
+        <v>0.02947331191606001</v>
       </c>
       <c r="W81">
-        <v>0.2287622208103221</v>
+        <v>0.2288501930501931</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1492319590686583</v>
+        <v>0.1473665595803</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2217309863583726</v>
+        <v>0.2236309863583726</v>
       </c>
       <c r="C82">
-        <v>-47.64492914268531</v>
+        <v>-48.55703290115224</v>
       </c>
       <c r="D82">
-        <v>12.64507085731469</v>
+        <v>12.50996709884776</v>
       </c>
       <c r="E82">
-        <v>50.26000000000001</v>
+        <v>51.03700000000001</v>
       </c>
       <c r="F82">
-        <v>62.16</v>
+        <v>62.937</v>
       </c>
       <c r="G82">
         <v>1.87</v>
@@ -8145,37 +8145,37 @@
         <v>2.16</v>
       </c>
       <c r="M82">
-        <v>14.657328</v>
+        <v>14.8405446</v>
       </c>
       <c r="N82">
-        <v>-12.497328</v>
+        <v>-12.6805446</v>
       </c>
       <c r="O82">
-        <v>-2.499465600000001</v>
+        <v>-2.53610892</v>
       </c>
       <c r="P82">
-        <v>-9.997862400000001</v>
+        <v>-10.14443568</v>
       </c>
       <c r="Q82">
-        <v>-8.797862400000001</v>
+        <v>-8.944435680000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1932541595910909</v>
+        <v>0.2010149048327273</v>
       </c>
       <c r="T82">
-        <v>2.87415602671328</v>
+        <v>3.025427396540294</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02947331191606001</v>
+        <v>0.02910944386771359</v>
       </c>
       <c r="W82">
-        <v>0.2288501930501931</v>
+        <v>0.2289359931359931</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1473665595803</v>
+        <v>0.145547219338568</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2236309863583726</v>
+        <v>0.2255309863583726</v>
       </c>
       <c r="C83">
-        <v>-48.55703290115224</v>
+        <v>-49.46628020012615</v>
       </c>
       <c r="D83">
-        <v>12.50996709884776</v>
+        <v>12.37771979987385</v>
       </c>
       <c r="E83">
-        <v>51.03700000000001</v>
+        <v>51.81400000000001</v>
       </c>
       <c r="F83">
-        <v>62.937</v>
+        <v>63.71400000000001</v>
       </c>
       <c r="G83">
         <v>1.87</v>
@@ -8227,37 +8227,37 @@
         <v>2.16</v>
       </c>
       <c r="M83">
-        <v>14.8405446</v>
+        <v>15.0237612</v>
       </c>
       <c r="N83">
-        <v>-12.6805446</v>
+        <v>-12.8637612</v>
       </c>
       <c r="O83">
-        <v>-2.53610892</v>
+        <v>-2.572752240000001</v>
       </c>
       <c r="P83">
-        <v>-10.14443568</v>
+        <v>-10.29100896</v>
       </c>
       <c r="Q83">
-        <v>-8.944435680000002</v>
+        <v>-9.091008960000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2010149048327273</v>
+        <v>0.2096379551012121</v>
       </c>
       <c r="T83">
-        <v>3.025427396540294</v>
+        <v>3.193506696348089</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02910944386771359</v>
+        <v>0.02875445064981464</v>
       </c>
       <c r="W83">
-        <v>0.2289359931359931</v>
+        <v>0.2290197005367737</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.145547219338568</v>
+        <v>0.1437722532490732</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2255309863583726</v>
+        <v>0.2274309863583726</v>
       </c>
       <c r="C84">
-        <v>-49.46628020012615</v>
+        <v>-50.37276068190562</v>
       </c>
       <c r="D84">
-        <v>12.37771979987385</v>
+        <v>12.24823931809439</v>
       </c>
       <c r="E84">
-        <v>51.81400000000001</v>
+        <v>52.59100000000002</v>
       </c>
       <c r="F84">
-        <v>63.71400000000001</v>
+        <v>64.49100000000001</v>
       </c>
       <c r="G84">
         <v>1.87</v>
@@ -8309,37 +8309,37 @@
         <v>2.16</v>
       </c>
       <c r="M84">
-        <v>15.0237612</v>
+        <v>15.2069778</v>
       </c>
       <c r="N84">
-        <v>-12.8637612</v>
+        <v>-13.0469778</v>
       </c>
       <c r="O84">
-        <v>-2.572752240000001</v>
+        <v>-2.609395560000001</v>
       </c>
       <c r="P84">
-        <v>-10.29100896</v>
+        <v>-10.43758224</v>
       </c>
       <c r="Q84">
-        <v>-9.091008960000003</v>
+        <v>-9.237582240000004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2096379551012121</v>
+        <v>0.2192754818718717</v>
       </c>
       <c r="T84">
-        <v>3.193506696348089</v>
+        <v>3.381360031427389</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02875445064981464</v>
+        <v>0.02840801148535904</v>
       </c>
       <c r="W84">
-        <v>0.2290197005367737</v>
+        <v>0.2291013908917524</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1437722532490732</v>
+        <v>0.1420400574267952</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2274309863583726</v>
+        <v>0.2293309863583726</v>
       </c>
       <c r="C85">
-        <v>-50.37276068190562</v>
+        <v>-51.27656027671048</v>
       </c>
       <c r="D85">
-        <v>12.24823931809439</v>
+        <v>12.12143972328953</v>
       </c>
       <c r="E85">
-        <v>52.59100000000002</v>
+        <v>53.36800000000002</v>
       </c>
       <c r="F85">
-        <v>64.49100000000001</v>
+        <v>65.26800000000001</v>
       </c>
       <c r="G85">
         <v>1.87</v>
@@ -8391,37 +8391,37 @@
         <v>2.16</v>
       </c>
       <c r="M85">
-        <v>15.2069778</v>
+        <v>15.3901944</v>
       </c>
       <c r="N85">
-        <v>-13.0469778</v>
+        <v>-13.2301944</v>
       </c>
       <c r="O85">
-        <v>-2.609395560000001</v>
+        <v>-2.646038880000001</v>
       </c>
       <c r="P85">
-        <v>-10.43758224</v>
+        <v>-10.58415552</v>
       </c>
       <c r="Q85">
-        <v>-9.237582240000004</v>
+        <v>-9.384155520000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2192754818718717</v>
+        <v>0.2301176994888637</v>
       </c>
       <c r="T85">
-        <v>3.381360031427389</v>
+        <v>3.592695033391601</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02840801148535904</v>
+        <v>0.0280698208724381</v>
       </c>
       <c r="W85">
-        <v>0.2291013908917524</v>
+        <v>0.2291811362382791</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1420400574267952</v>
+        <v>0.1403491043621905</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2293309863583726</v>
+        <v>0.2312309863583726</v>
       </c>
       <c r="C86">
-        <v>-51.27656027671047</v>
+        <v>-52.1777613928591</v>
       </c>
       <c r="D86">
-        <v>12.12143972328953</v>
+        <v>11.9972386071409</v>
       </c>
       <c r="E86">
-        <v>53.368</v>
+        <v>54.145</v>
       </c>
       <c r="F86">
-        <v>65.268</v>
+        <v>66.045</v>
       </c>
       <c r="G86">
         <v>1.87</v>
@@ -8473,37 +8473,37 @@
         <v>2.16</v>
       </c>
       <c r="M86">
-        <v>15.3901944</v>
+        <v>15.573411</v>
       </c>
       <c r="N86">
-        <v>-13.2301944</v>
+        <v>-13.413411</v>
       </c>
       <c r="O86">
-        <v>-2.64603888</v>
+        <v>-2.6826822</v>
       </c>
       <c r="P86">
-        <v>-10.58415552</v>
+        <v>-10.7307288</v>
       </c>
       <c r="Q86">
-        <v>-9.38415552</v>
+        <v>-9.530728800000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2301176994888636</v>
+        <v>0.2424055461214545</v>
       </c>
       <c r="T86">
-        <v>3.592695033391598</v>
+        <v>3.832208035617705</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02806982087243811</v>
+        <v>0.02773958768570354</v>
       </c>
       <c r="W86">
-        <v>0.2291811362382791</v>
+        <v>0.2292590052237111</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1403491043621905</v>
+        <v>0.1386979384285176</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2312309863583726</v>
+        <v>0.2331309863583726</v>
       </c>
       <c r="C87">
-        <v>-52.1777613928591</v>
+        <v>-53.07644309537232</v>
       </c>
       <c r="D87">
-        <v>11.9972386071409</v>
+        <v>11.87555690462768</v>
       </c>
       <c r="E87">
-        <v>54.145</v>
+        <v>54.922</v>
       </c>
       <c r="F87">
-        <v>66.045</v>
+        <v>66.822</v>
       </c>
       <c r="G87">
         <v>1.87</v>
@@ -8555,37 +8555,37 @@
         <v>2.16</v>
       </c>
       <c r="M87">
-        <v>15.573411</v>
+        <v>15.7566276</v>
       </c>
       <c r="N87">
-        <v>-13.413411</v>
+        <v>-13.5966276</v>
       </c>
       <c r="O87">
-        <v>-2.6826822</v>
+        <v>-2.71932552</v>
       </c>
       <c r="P87">
-        <v>-10.7307288</v>
+        <v>-10.87730208</v>
       </c>
       <c r="Q87">
-        <v>-9.530728800000002</v>
+        <v>-9.677302080000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2424055461214545</v>
+        <v>0.2564487994158441</v>
       </c>
       <c r="T87">
-        <v>3.832208035617705</v>
+        <v>4.10593718101897</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02773958768570354</v>
+        <v>0.02741703434052094</v>
       </c>
       <c r="W87">
-        <v>0.2292590052237111</v>
+        <v>0.2293350633025052</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1386979384285176</v>
+        <v>0.1370851717026047</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2331309863583726</v>
+        <v>0.2350309863583726</v>
       </c>
       <c r="C88">
-        <v>-53.07644309537232</v>
+        <v>-53.97268127381768</v>
       </c>
       <c r="D88">
-        <v>11.87555690462768</v>
+        <v>11.75631872618232</v>
       </c>
       <c r="E88">
-        <v>54.922</v>
+        <v>55.69900000000001</v>
       </c>
       <c r="F88">
-        <v>66.822</v>
+        <v>67.599</v>
       </c>
       <c r="G88">
         <v>1.87</v>
@@ -8637,37 +8637,37 @@
         <v>2.16</v>
       </c>
       <c r="M88">
-        <v>15.7566276</v>
+        <v>15.9398442</v>
       </c>
       <c r="N88">
-        <v>-13.5966276</v>
+        <v>-13.7798442</v>
       </c>
       <c r="O88">
-        <v>-2.71932552</v>
+        <v>-2.75596884</v>
       </c>
       <c r="P88">
-        <v>-10.87730208</v>
+        <v>-11.02387536</v>
       </c>
       <c r="Q88">
-        <v>-9.677302080000002</v>
+        <v>-9.823875360000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2564487994158441</v>
+        <v>0.2726525532170628</v>
       </c>
       <c r="T88">
-        <v>4.10593718101897</v>
+        <v>4.421778502635814</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02741703434052094</v>
+        <v>0.02710189601476783</v>
       </c>
       <c r="W88">
-        <v>0.2293350633025052</v>
+        <v>0.2294093729197177</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1370851717026047</v>
+        <v>0.1355094800738391</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2350309863583726</v>
+        <v>0.2369309863583726</v>
       </c>
       <c r="C89">
-        <v>-53.97268127381768</v>
+        <v>-54.86654880014261</v>
       </c>
       <c r="D89">
-        <v>11.75631872618232</v>
+        <v>11.63945119985739</v>
       </c>
       <c r="E89">
-        <v>55.69900000000001</v>
+        <v>56.47600000000001</v>
       </c>
       <c r="F89">
-        <v>67.599</v>
+        <v>68.376</v>
       </c>
       <c r="G89">
         <v>1.87</v>
@@ -8719,37 +8719,37 @@
         <v>2.16</v>
       </c>
       <c r="M89">
-        <v>15.9398442</v>
+        <v>16.1230608</v>
       </c>
       <c r="N89">
-        <v>-13.7798442</v>
+        <v>-13.9630608</v>
       </c>
       <c r="O89">
-        <v>-2.75596884</v>
+        <v>-2.79261216</v>
       </c>
       <c r="P89">
-        <v>-11.02387536</v>
+        <v>-11.17044864</v>
       </c>
       <c r="Q89">
-        <v>-9.823875360000002</v>
+        <v>-9.970448640000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2726525532170628</v>
+        <v>0.2915569326518181</v>
       </c>
       <c r="T89">
-        <v>4.421778502635814</v>
+        <v>4.790260044522133</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02710189601476783</v>
+        <v>0.02679391992369092</v>
       </c>
       <c r="W89">
-        <v>0.2294093729197177</v>
+        <v>0.2294819936819937</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1355094800738391</v>
+        <v>0.1339695996184546</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2369309863583726</v>
+        <v>0.2388309863583726</v>
       </c>
       <c r="C90">
-        <v>-54.86654880014261</v>
+        <v>-55.75811567718625</v>
       </c>
       <c r="D90">
-        <v>11.63945119985739</v>
+        <v>11.52488432281376</v>
       </c>
       <c r="E90">
-        <v>56.47600000000001</v>
+        <v>57.25300000000001</v>
       </c>
       <c r="F90">
-        <v>68.376</v>
+        <v>69.15300000000001</v>
       </c>
       <c r="G90">
         <v>1.87</v>
@@ -8801,37 +8801,37 @@
         <v>2.16</v>
       </c>
       <c r="M90">
-        <v>16.1230608</v>
+        <v>16.3062774</v>
       </c>
       <c r="N90">
-        <v>-13.9630608</v>
+        <v>-14.1462774</v>
       </c>
       <c r="O90">
-        <v>-2.79261216</v>
+        <v>-2.82925548</v>
       </c>
       <c r="P90">
-        <v>-11.17044864</v>
+        <v>-11.31702192</v>
       </c>
       <c r="Q90">
-        <v>-9.970448640000001</v>
+        <v>-10.11702192</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2915569326518181</v>
+        <v>0.3138984719838017</v>
       </c>
       <c r="T90">
-        <v>4.790260044522133</v>
+        <v>5.225738230387782</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02679391992369092</v>
+        <v>0.02649286464364944</v>
       </c>
       <c r="W90">
-        <v>0.2294819936819937</v>
+        <v>0.2295529825170275</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1339695996184546</v>
+        <v>0.1324643232182472</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2388309863583726</v>
+        <v>0.2407309863583726</v>
       </c>
       <c r="C91">
-        <v>-55.75811567718625</v>
+        <v>-56.64744917850598</v>
       </c>
       <c r="D91">
-        <v>11.52488432281376</v>
+        <v>11.41255082149402</v>
       </c>
       <c r="E91">
-        <v>57.25300000000001</v>
+        <v>58.03000000000001</v>
       </c>
       <c r="F91">
-        <v>69.15300000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="G91">
         <v>1.87</v>
@@ -8883,37 +8883,37 @@
         <v>2.16</v>
       </c>
       <c r="M91">
-        <v>16.3062774</v>
+        <v>16.489494</v>
       </c>
       <c r="N91">
-        <v>-14.1462774</v>
+        <v>-14.329494</v>
       </c>
       <c r="O91">
-        <v>-2.82925548</v>
+        <v>-2.8658988</v>
       </c>
       <c r="P91">
-        <v>-11.31702192</v>
+        <v>-11.4635952</v>
       </c>
       <c r="Q91">
-        <v>-10.11702192</v>
+        <v>-10.2635952</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3138984719838017</v>
+        <v>0.3407083191821818</v>
       </c>
       <c r="T91">
-        <v>5.225738230387782</v>
+        <v>5.748312053426559</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02649286464364944</v>
+        <v>0.02619849948094223</v>
       </c>
       <c r="W91">
-        <v>0.2295529825170275</v>
+        <v>0.2296223938223938</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1324643232182472</v>
+        <v>0.1309924974047112</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2407309863583726</v>
+        <v>0.2426309863583726</v>
       </c>
       <c r="C92">
-        <v>-56.64744917850598</v>
+        <v>-57.53461398010566</v>
       </c>
       <c r="D92">
-        <v>11.41255082149402</v>
+        <v>11.30238601989435</v>
       </c>
       <c r="E92">
-        <v>58.03000000000001</v>
+        <v>58.80700000000001</v>
       </c>
       <c r="F92">
-        <v>69.93000000000001</v>
+        <v>70.70700000000001</v>
       </c>
       <c r="G92">
         <v>1.87</v>
@@ -8965,37 +8965,37 @@
         <v>2.16</v>
       </c>
       <c r="M92">
-        <v>16.489494</v>
+        <v>16.6727106</v>
       </c>
       <c r="N92">
-        <v>-14.329494</v>
+        <v>-14.5127106</v>
       </c>
       <c r="O92">
-        <v>-2.8658988</v>
+        <v>-2.902542120000001</v>
       </c>
       <c r="P92">
-        <v>-11.4635952</v>
+        <v>-11.61016848</v>
       </c>
       <c r="Q92">
-        <v>-10.2635952</v>
+        <v>-10.41016848</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3407083191821818</v>
+        <v>0.3734759102024243</v>
       </c>
       <c r="T92">
-        <v>5.748312053426559</v>
+        <v>6.387013392696177</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02619849948094223</v>
+        <v>0.02591060388225055</v>
       </c>
       <c r="W92">
-        <v>0.2296223938223938</v>
+        <v>0.2296902796045653</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1309924974047112</v>
+        <v>0.1295530194112527</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2426309863583726</v>
+        <v>0.2445309863583726</v>
       </c>
       <c r="C93">
-        <v>-57.53461398010566</v>
+        <v>-58.41967228460717</v>
       </c>
       <c r="D93">
-        <v>11.30238601989435</v>
+        <v>11.19432771539283</v>
       </c>
       <c r="E93">
-        <v>58.80700000000001</v>
+        <v>59.58400000000001</v>
       </c>
       <c r="F93">
-        <v>70.70700000000001</v>
+        <v>71.48400000000001</v>
       </c>
       <c r="G93">
         <v>1.87</v>
@@ -9047,37 +9047,37 @@
         <v>2.16</v>
       </c>
       <c r="M93">
-        <v>16.6727106</v>
+        <v>16.8559272</v>
       </c>
       <c r="N93">
-        <v>-14.5127106</v>
+        <v>-14.6959272</v>
       </c>
       <c r="O93">
-        <v>-2.902542120000001</v>
+        <v>-2.939185440000001</v>
       </c>
       <c r="P93">
-        <v>-11.61016848</v>
+        <v>-11.75674176</v>
       </c>
       <c r="Q93">
-        <v>-10.41016848</v>
+        <v>-10.55674176</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3734759102024243</v>
+        <v>0.4144353989777274</v>
       </c>
       <c r="T93">
-        <v>6.387013392696177</v>
+        <v>7.185390066783202</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02591060388225055</v>
+        <v>0.02562896688353044</v>
       </c>
       <c r="W93">
-        <v>0.2296902796045653</v>
+        <v>0.2297566896088635</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1295530194112527</v>
+        <v>0.1281448344176522</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2445309863583726</v>
+        <v>0.2464309863583727</v>
       </c>
       <c r="C94">
-        <v>-58.41967228460717</v>
+        <v>-59.30268393836666</v>
       </c>
       <c r="D94">
-        <v>11.19432771539283</v>
+        <v>11.08831606163336</v>
       </c>
       <c r="E94">
-        <v>59.58400000000001</v>
+        <v>60.36100000000001</v>
       </c>
       <c r="F94">
-        <v>71.48400000000001</v>
+        <v>72.26100000000001</v>
       </c>
       <c r="G94">
         <v>1.87</v>
@@ -9129,37 +9129,37 @@
         <v>2.16</v>
       </c>
       <c r="M94">
-        <v>16.8559272</v>
+        <v>17.0391438</v>
       </c>
       <c r="N94">
-        <v>-14.6959272</v>
+        <v>-14.8791438</v>
       </c>
       <c r="O94">
-        <v>-2.939185440000001</v>
+        <v>-2.975828760000001</v>
       </c>
       <c r="P94">
-        <v>-11.75674176</v>
+        <v>-11.90331504</v>
       </c>
       <c r="Q94">
-        <v>-10.55674176</v>
+        <v>-10.70331504</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4144353989777274</v>
+        <v>0.4670975988316885</v>
       </c>
       <c r="T94">
-        <v>7.185390066783202</v>
+        <v>8.211874362037946</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02562896688353044</v>
+        <v>0.02535338659446022</v>
       </c>
       <c r="W94">
-        <v>0.2297566896088635</v>
+        <v>0.2298216714410263</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1281448344176522</v>
+        <v>0.1267669329723011</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2464309863583727</v>
+        <v>0.2483309863583726</v>
       </c>
       <c r="C95">
-        <v>-59.30268393836666</v>
+        <v>-60.1837065419984</v>
       </c>
       <c r="D95">
-        <v>11.08831606163336</v>
+        <v>10.98429345800161</v>
       </c>
       <c r="E95">
-        <v>60.36100000000001</v>
+        <v>61.13800000000001</v>
       </c>
       <c r="F95">
-        <v>72.26100000000001</v>
+        <v>73.03800000000001</v>
       </c>
       <c r="G95">
         <v>1.87</v>
@@ -9211,37 +9211,37 @@
         <v>2.16</v>
       </c>
       <c r="M95">
-        <v>17.0391438</v>
+        <v>17.2223604</v>
       </c>
       <c r="N95">
-        <v>-14.8791438</v>
+        <v>-15.0623604</v>
       </c>
       <c r="O95">
-        <v>-2.975828760000001</v>
+        <v>-3.012472080000001</v>
       </c>
       <c r="P95">
-        <v>-11.90331504</v>
+        <v>-12.04988832</v>
       </c>
       <c r="Q95">
-        <v>-10.70331504</v>
+        <v>-10.84988832</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4670975988316885</v>
+        <v>0.5373138653036368</v>
       </c>
       <c r="T95">
-        <v>8.211874362037946</v>
+        <v>9.580520089044274</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02535338659446022</v>
+        <v>0.02508366971579575</v>
       </c>
       <c r="W95">
-        <v>0.2298216714410263</v>
+        <v>0.2298852706810154</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1267669329723011</v>
+        <v>0.1254183485789787</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2483309863583726</v>
+        <v>0.2502309863583727</v>
       </c>
       <c r="C96">
-        <v>-60.1837065419984</v>
+        <v>-61.06279555473553</v>
       </c>
       <c r="D96">
-        <v>10.98429345800161</v>
+        <v>10.88220444526448</v>
       </c>
       <c r="E96">
-        <v>61.13800000000001</v>
+        <v>61.91500000000001</v>
       </c>
       <c r="F96">
-        <v>73.03800000000001</v>
+        <v>73.81500000000001</v>
       </c>
       <c r="G96">
         <v>1.87</v>
@@ -9293,37 +9293,37 @@
         <v>2.16</v>
       </c>
       <c r="M96">
-        <v>17.2223604</v>
+        <v>17.405577</v>
       </c>
       <c r="N96">
-        <v>-15.0623604</v>
+        <v>-15.245577</v>
       </c>
       <c r="O96">
-        <v>-3.012472080000001</v>
+        <v>-3.049115400000001</v>
       </c>
       <c r="P96">
-        <v>-12.04988832</v>
+        <v>-12.1964616</v>
       </c>
       <c r="Q96">
-        <v>-10.84988832</v>
+        <v>-10.9964616</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5373138653036368</v>
+        <v>0.6356166383643643</v>
       </c>
       <c r="T96">
-        <v>9.580520089044274</v>
+        <v>11.49662410685313</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02508366971579575</v>
+        <v>0.02481963108720842</v>
       </c>
       <c r="W96">
-        <v>0.2298852706810154</v>
+        <v>0.2299475309896363</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1254183485789787</v>
+        <v>0.1240981554360421</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2502309863583727</v>
+        <v>0.2521309863583726</v>
       </c>
       <c r="C97">
-        <v>-61.06279555473553</v>
+        <v>-61.94000439302456</v>
       </c>
       <c r="D97">
-        <v>10.88220444526448</v>
+        <v>10.78199560697545</v>
       </c>
       <c r="E97">
-        <v>61.91500000000001</v>
+        <v>62.69200000000001</v>
       </c>
       <c r="F97">
-        <v>73.81500000000001</v>
+        <v>74.59200000000001</v>
       </c>
       <c r="G97">
         <v>1.87</v>
@@ -9375,37 +9375,37 @@
         <v>2.16</v>
       </c>
       <c r="M97">
-        <v>17.405577</v>
+        <v>17.5887936</v>
       </c>
       <c r="N97">
-        <v>-15.245577</v>
+        <v>-15.4287936</v>
       </c>
       <c r="O97">
-        <v>-3.049115400000001</v>
+        <v>-3.085758720000001</v>
       </c>
       <c r="P97">
-        <v>-12.1964616</v>
+        <v>-12.34303488</v>
       </c>
       <c r="Q97">
-        <v>-10.9964616</v>
+        <v>-11.14303488</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6356166383643643</v>
+        <v>0.7830707979554556</v>
       </c>
       <c r="T97">
-        <v>11.49662410685313</v>
+        <v>14.37078013356642</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02481963108720842</v>
+        <v>0.02456109326338334</v>
       </c>
       <c r="W97">
-        <v>0.2299475309896363</v>
+        <v>0.2300084942084942</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1240981554360421</v>
+        <v>0.1228054663169167</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2521309863583726</v>
+        <v>0.2540309863583726</v>
       </c>
       <c r="C98">
-        <v>-61.94000439302454</v>
+        <v>-62.81538452372227</v>
       </c>
       <c r="D98">
-        <v>10.78199560697545</v>
+        <v>10.68361547627773</v>
       </c>
       <c r="E98">
-        <v>62.692</v>
+        <v>63.469</v>
       </c>
       <c r="F98">
-        <v>74.592</v>
+        <v>75.369</v>
       </c>
       <c r="G98">
         <v>1.87</v>
@@ -9457,37 +9457,37 @@
         <v>2.16</v>
       </c>
       <c r="M98">
-        <v>17.5887936</v>
+        <v>17.7720102</v>
       </c>
       <c r="N98">
-        <v>-15.4287936</v>
+        <v>-15.6120102</v>
       </c>
       <c r="O98">
-        <v>-3.08575872</v>
+        <v>-3.12240204</v>
       </c>
       <c r="P98">
-        <v>-12.34303488</v>
+        <v>-12.48960816</v>
       </c>
       <c r="Q98">
-        <v>-11.14303488</v>
+        <v>-11.28960816</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7830707979554538</v>
+        <v>1.028827730607272</v>
       </c>
       <c r="T98">
-        <v>14.37078013356638</v>
+        <v>19.16104017808851</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02456109326338335</v>
+        <v>0.02430788611633815</v>
       </c>
       <c r="W98">
-        <v>0.2300084942084942</v>
+        <v>0.2300682004537675</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1228054663169167</v>
+        <v>0.1215394305816908</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2540309863583726</v>
+        <v>0.2559309863583726</v>
       </c>
       <c r="C99">
-        <v>-62.81538452372227</v>
+        <v>-63.6889855522365</v>
       </c>
       <c r="D99">
-        <v>10.68361547627773</v>
+        <v>10.5870144477635</v>
       </c>
       <c r="E99">
-        <v>63.469</v>
+        <v>64.246</v>
       </c>
       <c r="F99">
-        <v>75.369</v>
+        <v>76.146</v>
       </c>
       <c r="G99">
         <v>1.87</v>
@@ -9539,37 +9539,37 @@
         <v>2.16</v>
       </c>
       <c r="M99">
-        <v>17.7720102</v>
+        <v>17.9552268</v>
       </c>
       <c r="N99">
-        <v>-15.6120102</v>
+        <v>-15.7952268</v>
       </c>
       <c r="O99">
-        <v>-3.12240204</v>
+        <v>-3.15904536</v>
       </c>
       <c r="P99">
-        <v>-12.48960816</v>
+        <v>-12.63618144</v>
       </c>
       <c r="Q99">
-        <v>-11.28960816</v>
+        <v>-11.43618144</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.028827730607272</v>
+        <v>1.520341595910907</v>
       </c>
       <c r="T99">
-        <v>19.16104017808851</v>
+        <v>28.74156026713277</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02430788611633815</v>
+        <v>0.0240598464620898</v>
       </c>
       <c r="W99">
-        <v>0.2300682004537675</v>
+        <v>0.2301266882042392</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1215394305816908</v>
+        <v>0.120299232310449</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2559309863583726</v>
+        <v>0.2578309863583726</v>
       </c>
       <c r="C100">
-        <v>-63.6889855522365</v>
+        <v>-64.56085530592784</v>
       </c>
       <c r="D100">
-        <v>10.5870144477635</v>
+        <v>10.49214469407216</v>
       </c>
       <c r="E100">
-        <v>64.246</v>
+        <v>65.023</v>
       </c>
       <c r="F100">
-        <v>76.146</v>
+        <v>76.923</v>
       </c>
       <c r="G100">
         <v>1.87</v>
@@ -9621,37 +9621,37 @@
         <v>2.16</v>
       </c>
       <c r="M100">
-        <v>17.9552268</v>
+        <v>18.1384434</v>
       </c>
       <c r="N100">
-        <v>-15.7952268</v>
+        <v>-15.9784434</v>
       </c>
       <c r="O100">
-        <v>-3.15904536</v>
+        <v>-3.19568868</v>
       </c>
       <c r="P100">
-        <v>-12.63618144</v>
+        <v>-12.78275472</v>
       </c>
       <c r="Q100">
-        <v>-11.43618144</v>
+        <v>-11.58275472</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.520341595910907</v>
+        <v>2.994883191821815</v>
       </c>
       <c r="T100">
-        <v>28.74156026713277</v>
+        <v>57.48312053426553</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0240598464620898</v>
+        <v>0.02381681770994748</v>
       </c>
       <c r="W100">
-        <v>0.2301266882042392</v>
+        <v>0.2301839943839944</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.120299232310449</v>
+        <v>0.1190840885497374</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2578309863583726</v>
-      </c>
-      <c r="C101">
-        <v>-64.56085530592784</v>
-      </c>
-      <c r="D101">
-        <v>10.49214469407216</v>
-      </c>
-      <c r="E101">
-        <v>65.023</v>
-      </c>
-      <c r="F101">
-        <v>76.923</v>
-      </c>
-      <c r="G101">
-        <v>1.87</v>
-      </c>
-      <c r="H101">
-        <v>65.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.36</v>
-      </c>
-      <c r="K101">
-        <v>1.2</v>
-      </c>
-      <c r="L101">
-        <v>2.16</v>
-      </c>
-      <c r="M101">
-        <v>18.1384434</v>
-      </c>
-      <c r="N101">
-        <v>-15.9784434</v>
-      </c>
-      <c r="O101">
-        <v>-3.19568868</v>
-      </c>
-      <c r="P101">
-        <v>-12.78275472</v>
-      </c>
-      <c r="Q101">
-        <v>-11.58275472</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.994883191821815</v>
-      </c>
-      <c r="T101">
-        <v>57.48312053426553</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02381681770994748</v>
-      </c>
-      <c r="W101">
-        <v>0.2301839943839944</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1190840885497374</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
